--- a/jogos_2026-10-07.xlsx
+++ b/jogos_2026-10-07.xlsx
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G19">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G20">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G21">

--- a/jogos_2026-10-07.xlsx
+++ b/jogos_2026-10-07.xlsx
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Temouchent</t>
         </is>
       </c>
       <c r="G22">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G23">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>US Biskra</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G24">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Temouchent</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G27">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G28">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>US Biskra</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G29">

--- a/jogos_2026-10-07.xlsx
+++ b/jogos_2026-10-07.xlsx
@@ -4217,7 +4217,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N24">
@@ -4380,7 +4380,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N25">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>JS El Biar</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G26">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G27">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G28">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>JS El Biar</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G29">

--- a/jogos_2026-10-07.xlsx
+++ b/jogos_2026-10-07.xlsx
@@ -2600,55 +2600,55 @@
         <v>0</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q15">
         <v>0</v>
@@ -2793,10 +2793,10 @@
         <v>0</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC15">
         <v>0</v>
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -3445,10 +3445,10 @@
         <v>0</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC19">
         <v>0</v>
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AL21">
         <v>0</v>

--- a/jogos_2026-10-07.xlsx
+++ b/jogos_2026-10-07.xlsx
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.61</v>
+        <v>2.18</v>
       </c>
       <c r="O11">
-        <v>3.37</v>
+        <v>3.3</v>
       </c>
       <c r="P11">
-        <v>2.77</v>
+        <v>3.57</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA11">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="AB11">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2274,34 +2274,34 @@
         <v>4.59</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA12">
         <v>1.78</v>
@@ -2310,19 +2310,19 @@
         <v>1.9</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,80 +2428,80 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.18</v>
+        <v>2.61</v>
       </c>
       <c r="O13">
-        <v>3.3</v>
+        <v>3.37</v>
       </c>
       <c r="P13">
-        <v>3.57</v>
+        <v>2.77</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA13">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="AB13">
+        <v>1.72</v>
+      </c>
+      <c r="AC13">
+        <v>3.25</v>
+      </c>
+      <c r="AD13">
+        <v>1.3</v>
+      </c>
+      <c r="AE13">
+        <v>1.07</v>
+      </c>
+      <c r="AF13">
+        <v>1.67</v>
+      </c>
+      <c r="AG13">
+        <v>2.1</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ13">
+        <v>1.29</v>
+      </c>
+      <c r="AK13">
         <v>1.6</v>
-      </c>
-      <c r="AC13">
-        <v>0</v>
-      </c>
-      <c r="AD13">
-        <v>0</v>
-      </c>
-      <c r="AE13">
-        <v>0</v>
-      </c>
-      <c r="AF13">
-        <v>0</v>
-      </c>
-      <c r="AG13">
-        <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ13">
-        <v>0</v>
-      </c>
-      <c r="AK13">
-        <v>0</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2926,34 +2926,34 @@
         <v>5.25</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA16">
         <v>1.88</v>
@@ -2962,19 +2962,19 @@
         <v>1.8</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3252,34 +3252,34 @@
         <v>3.18</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA18">
         <v>1.9</v>
@@ -3288,19 +3288,19 @@
         <v>1.78</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G27">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G28">
@@ -5208,34 +5208,34 @@
         <v>4.47</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W30">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X30">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y30">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z30">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA30">
         <v>1.98</v>
@@ -5244,19 +5244,19 @@
         <v>1.72</v>
       </c>
       <c r="AC30">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG30">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK30">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AL30">
         <v>0</v>

--- a/jogos_2026-10-07.xlsx
+++ b/jogos_2026-10-07.xlsx
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>3.2</v>
+        <v>1.95</v>
       </c>
       <c r="O20">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P20">
-        <v>2.1</v>
+        <v>3.4</v>
       </c>
       <c r="Q20">
-        <v>4.37</v>
+        <v>2.65</v>
       </c>
       <c r="R20">
-        <v>2.18</v>
+        <v>2.23</v>
       </c>
       <c r="S20">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="T20">
-        <v>2.81</v>
+        <v>2.95</v>
       </c>
       <c r="U20">
-        <v>3.06</v>
+        <v>2.9</v>
       </c>
       <c r="V20">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="W20">
+        <v>1.05</v>
+      </c>
+      <c r="X20">
         <v>1.03</v>
       </c>
-      <c r="X20">
-        <v>1.02</v>
-      </c>
       <c r="Y20">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="Z20">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AA20">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AB20">
+        <v>1.75</v>
+      </c>
+      <c r="AC20">
+        <v>3.39</v>
+      </c>
+      <c r="AD20">
+        <v>1.31</v>
+      </c>
+      <c r="AE20">
+        <v>1.11</v>
+      </c>
+      <c r="AF20">
         <v>1.76</v>
       </c>
-      <c r="AC20">
-        <v>3.69</v>
-      </c>
-      <c r="AD20">
-        <v>1.27</v>
-      </c>
-      <c r="AE20">
-        <v>1.05</v>
-      </c>
-      <c r="AF20">
-        <v>1.83</v>
-      </c>
       <c r="AG20">
-        <v>1.87</v>
+        <v>1.96</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AK20">
-        <v>1.27</v>
+        <v>1.74</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.95</v>
+        <v>3.2</v>
       </c>
       <c r="O21">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P21">
-        <v>3.4</v>
+        <v>2.1</v>
       </c>
       <c r="Q21">
-        <v>2.65</v>
+        <v>4.37</v>
       </c>
       <c r="R21">
-        <v>2.23</v>
+        <v>2.18</v>
       </c>
       <c r="S21">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="T21">
-        <v>2.95</v>
+        <v>2.81</v>
       </c>
       <c r="U21">
-        <v>2.9</v>
+        <v>3.06</v>
       </c>
       <c r="V21">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="W21">
+        <v>1.03</v>
+      </c>
+      <c r="X21">
+        <v>1.02</v>
+      </c>
+      <c r="Y21">
+        <v>1.34</v>
+      </c>
+      <c r="Z21">
+        <v>3.2</v>
+      </c>
+      <c r="AA21">
+        <v>2.2</v>
+      </c>
+      <c r="AB21">
+        <v>1.76</v>
+      </c>
+      <c r="AC21">
+        <v>3.69</v>
+      </c>
+      <c r="AD21">
+        <v>1.27</v>
+      </c>
+      <c r="AE21">
         <v>1.05</v>
       </c>
-      <c r="X21">
-        <v>1.03</v>
-      </c>
-      <c r="Y21">
-        <v>1.3</v>
-      </c>
-      <c r="Z21">
-        <v>3.25</v>
-      </c>
-      <c r="AA21">
-        <v>2.05</v>
-      </c>
-      <c r="AB21">
-        <v>1.75</v>
-      </c>
-      <c r="AC21">
-        <v>3.39</v>
-      </c>
-      <c r="AD21">
-        <v>1.31</v>
-      </c>
-      <c r="AE21">
-        <v>1.11</v>
-      </c>
       <c r="AF21">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AG21">
-        <v>1.96</v>
+        <v>1.87</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AK21">
-        <v>1.74</v>
+        <v>1.27</v>
       </c>
       <c r="AL21">
         <v>0</v>

--- a/jogos_2026-10-07.xlsx
+++ b/jogos_2026-10-07.xlsx
@@ -2600,55 +2600,55 @@
         <v>0</v>
       </c>
       <c r="Q14">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="R14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S14">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T14">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U14">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="V14">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W14">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X14">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y14">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z14">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AA14">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB14">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC14">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="AD14">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE14">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF14">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG14">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK14">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G26">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>JS El Biar</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G27">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G28">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>JS El Biar</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G29">

--- a/jogos_2026-10-07.xlsx
+++ b/jogos_2026-10-07.xlsx
@@ -2600,55 +2600,55 @@
         <v>0</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2763,34 +2763,34 @@
         <v>3.9</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA15">
         <v>2.2</v>
@@ -2799,19 +2799,19 @@
         <v>1.65</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G19">
@@ -3409,61 +3409,61 @@
         <v>1.95</v>
       </c>
       <c r="O19">
-        <v>3.44</v>
+        <v>3.25</v>
       </c>
       <c r="P19">
-        <v>4.04</v>
+        <v>3.4</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA19">
-        <v>2.6</v>
+        <v>2.05</v>
       </c>
       <c r="AB19">
-        <v>1.47</v>
+        <v>1.75</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.95</v>
+        <v>3.2</v>
       </c>
       <c r="O20">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P20">
-        <v>3.4</v>
+        <v>2.1</v>
       </c>
       <c r="Q20">
-        <v>2.65</v>
+        <v>4.37</v>
       </c>
       <c r="R20">
-        <v>2.23</v>
+        <v>2.18</v>
       </c>
       <c r="S20">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="T20">
-        <v>2.95</v>
+        <v>2.81</v>
       </c>
       <c r="U20">
-        <v>2.9</v>
+        <v>3.06</v>
       </c>
       <c r="V20">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="W20">
+        <v>1.03</v>
+      </c>
+      <c r="X20">
+        <v>1.02</v>
+      </c>
+      <c r="Y20">
+        <v>1.34</v>
+      </c>
+      <c r="Z20">
+        <v>3.2</v>
+      </c>
+      <c r="AA20">
+        <v>2.2</v>
+      </c>
+      <c r="AB20">
+        <v>1.76</v>
+      </c>
+      <c r="AC20">
+        <v>3.69</v>
+      </c>
+      <c r="AD20">
+        <v>1.27</v>
+      </c>
+      <c r="AE20">
         <v>1.05</v>
       </c>
-      <c r="X20">
-        <v>1.03</v>
-      </c>
-      <c r="Y20">
-        <v>1.3</v>
-      </c>
-      <c r="Z20">
-        <v>3.25</v>
-      </c>
-      <c r="AA20">
-        <v>2.05</v>
-      </c>
-      <c r="AB20">
-        <v>1.75</v>
-      </c>
-      <c r="AC20">
-        <v>3.39</v>
-      </c>
-      <c r="AD20">
-        <v>1.31</v>
-      </c>
-      <c r="AE20">
-        <v>1.11</v>
-      </c>
       <c r="AF20">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AG20">
-        <v>1.96</v>
+        <v>1.87</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AK20">
-        <v>1.74</v>
+        <v>1.27</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>3.2</v>
+        <v>1.95</v>
       </c>
       <c r="O21">
-        <v>3.1</v>
+        <v>3.44</v>
       </c>
       <c r="P21">
-        <v>2.1</v>
+        <v>4.04</v>
       </c>
       <c r="Q21">
-        <v>4.37</v>
+        <v>2.78</v>
       </c>
       <c r="R21">
-        <v>2.18</v>
+        <v>2.03</v>
       </c>
       <c r="S21">
-        <v>1.4</v>
+        <v>1.56</v>
       </c>
       <c r="T21">
-        <v>2.81</v>
+        <v>2.39</v>
       </c>
       <c r="U21">
-        <v>3.06</v>
+        <v>3.4</v>
       </c>
       <c r="V21">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="W21">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X21">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y21">
-        <v>1.34</v>
+        <v>1.48</v>
       </c>
       <c r="Z21">
-        <v>3.2</v>
+        <v>2.59</v>
       </c>
       <c r="AA21">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="AB21">
-        <v>1.76</v>
+        <v>1.47</v>
       </c>
       <c r="AC21">
-        <v>3.69</v>
+        <v>4.43</v>
       </c>
       <c r="AD21">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="AE21">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF21">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="AG21">
-        <v>1.87</v>
+        <v>1.63</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AK21">
-        <v>1.27</v>
+        <v>1.78</v>
       </c>
       <c r="AL21">
         <v>0</v>

--- a/jogos_2026-10-07.xlsx
+++ b/jogos_2026-10-07.xlsx
@@ -2600,55 +2600,55 @@
         <v>0</v>
       </c>
       <c r="Q14">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="R14">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="S14">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="T14">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U14">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="V14">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W14">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X14">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y14">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Z14">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AA14">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB14">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC14">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="AD14">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AE14">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF14">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG14">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK14">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL14">
         <v>0</v>

--- a/jogos_2026-10-07.xlsx
+++ b/jogos_2026-10-07.xlsx
@@ -2102,19 +2102,19 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.18</v>
+        <v>2.13</v>
       </c>
       <c r="O11">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P11">
-        <v>3.57</v>
+        <v>3.4</v>
       </c>
       <c r="Q11">
         <v>2.7</v>
       </c>
       <c r="R11">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="S11">
         <v>1.4</v>
@@ -2141,13 +2141,13 @@
         <v>3.1</v>
       </c>
       <c r="AA11">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB11">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AC11">
-        <v>3.9</v>
+        <v>3.87</v>
       </c>
       <c r="AD11">
         <v>1.22</v>
@@ -2156,7 +2156,7 @@
         <v>1.05</v>
       </c>
       <c r="AF11">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG11">
         <v>1.85</v>
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="O12">
-        <v>3.71</v>
+        <v>3.8</v>
       </c>
       <c r="P12">
-        <v>4.59</v>
+        <v>3.85</v>
       </c>
       <c r="Q12">
         <v>2.27</v>
@@ -2304,10 +2304,10 @@
         <v>3.58</v>
       </c>
       <c r="AA12">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AB12">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC12">
         <v>3.1</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.61</v>
+        <v>2.2</v>
       </c>
       <c r="O13">
-        <v>3.37</v>
+        <v>3.5</v>
       </c>
       <c r="P13">
-        <v>2.77</v>
+        <v>3.2</v>
       </c>
       <c r="Q13">
         <v>2.56</v>
@@ -2449,10 +2449,10 @@
         <v>2.73</v>
       </c>
       <c r="U13">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="V13">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W13">
         <v>1.06</v>
@@ -2467,10 +2467,10 @@
         <v>3.6</v>
       </c>
       <c r="AA13">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="AB13">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="AC13">
         <v>3.25</v>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK13">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2600,55 +2600,55 @@
         <v>0</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,43 +2754,43 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="O15">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P15">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="Q15">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="R15">
         <v>2.05</v>
       </c>
       <c r="S15">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="T15">
-        <v>2.71</v>
+        <v>2.67</v>
       </c>
       <c r="U15">
-        <v>2.95</v>
+        <v>2.91</v>
       </c>
       <c r="V15">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W15">
         <v>1.04</v>
       </c>
       <c r="X15">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="Z15">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AA15">
         <v>2.2</v>
@@ -2799,19 +2799,19 @@
         <v>1.65</v>
       </c>
       <c r="AC15">
-        <v>4</v>
+        <v>4.03</v>
       </c>
       <c r="AD15">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AE15">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF15">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AG15">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>1.25</v>
       </c>
       <c r="AK15">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="O16">
-        <v>3.71</v>
+        <v>3.9</v>
       </c>
       <c r="P16">
-        <v>5.25</v>
+        <v>4.8</v>
       </c>
       <c r="Q16">
         <v>2.15</v>
@@ -2956,10 +2956,10 @@
         <v>3.42</v>
       </c>
       <c r="AA16">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AB16">
-        <v>1.8</v>
+        <v>1.94</v>
       </c>
       <c r="AC16">
         <v>2.97</v>
@@ -2974,7 +2974,7 @@
         <v>1.8</v>
       </c>
       <c r="AG16">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>

--- a/jogos_2026-10-07.xlsx
+++ b/jogos_2026-10-07.xlsx
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q14">
-        <v>2.87</v>
+        <v>2.63</v>
       </c>
       <c r="R14">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="S14">
         <v>1.47</v>
       </c>
       <c r="T14">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="U14">
-        <v>3.1</v>
+        <v>2.91</v>
       </c>
       <c r="V14">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="W14">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X14">
         <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="Z14">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="AA14">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AB14">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AC14">
-        <v>3.79</v>
+        <v>4.03</v>
       </c>
       <c r="AD14">
         <v>1.23</v>
       </c>
       <c r="AE14">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF14">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AG14">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK14">
         <v>1.8</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O15">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P15">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="Q15">
-        <v>2.63</v>
+        <v>2.87</v>
       </c>
       <c r="R15">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="S15">
         <v>1.47</v>
       </c>
       <c r="T15">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="U15">
-        <v>2.91</v>
+        <v>3.1</v>
       </c>
       <c r="V15">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="W15">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X15">
         <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="Z15">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="AA15">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AB15">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AC15">
-        <v>4.03</v>
+        <v>3.79</v>
       </c>
       <c r="AD15">
         <v>1.23</v>
       </c>
       <c r="AE15">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF15">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AG15">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK15">
         <v>1.8</v>

--- a/jogos_2026-10-07.xlsx
+++ b/jogos_2026-10-07.xlsx
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -2591,16 +2591,16 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="O14">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P14">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="Q14">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="R14">
         <v>2.05</v>
@@ -2609,16 +2609,16 @@
         <v>1.47</v>
       </c>
       <c r="T14">
-        <v>2.67</v>
+        <v>2.73</v>
       </c>
       <c r="U14">
-        <v>2.91</v>
+        <v>2.87</v>
       </c>
       <c r="V14">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W14">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X14">
         <v>1.01</v>
@@ -2627,28 +2627,28 @@
         <v>1.38</v>
       </c>
       <c r="Z14">
-        <v>2.9</v>
+        <v>3.09</v>
       </c>
       <c r="AA14">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AB14">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AC14">
-        <v>4.03</v>
+        <v>3.87</v>
       </c>
       <c r="AD14">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE14">
         <v>1.03</v>
       </c>
       <c r="AF14">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AG14">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>1.25</v>
       </c>
       <c r="AK14">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2793,10 +2793,10 @@
         <v>2.87</v>
       </c>
       <c r="AA15">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="AB15">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AC15">
         <v>3.79</v>
@@ -2827,7 +2827,7 @@
         <v>1.3</v>
       </c>
       <c r="AK15">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="O17">
         <v>5.5</v>
       </c>
       <c r="P17">
-        <v>7.99</v>
+        <v>9</v>
       </c>
       <c r="Q17">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="R17">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="S17">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T17">
         <v>3.2</v>
       </c>
       <c r="U17">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="V17">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="W17">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X17">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y17">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="Z17">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="AA17">
-        <v>1.61</v>
+        <v>1.52</v>
       </c>
       <c r="AB17">
+        <v>2.5</v>
+      </c>
+      <c r="AC17">
         <v>2.2</v>
       </c>
-      <c r="AC17">
-        <v>2.55</v>
-      </c>
       <c r="AD17">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="AE17">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AF17">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AG17">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AK17">
-        <v>3.42</v>
+        <v>3.62</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3415,7 +3415,7 @@
         <v>3.4</v>
       </c>
       <c r="Q19">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="R19">
         <v>2.23</v>
@@ -3424,10 +3424,10 @@
         <v>1.37</v>
       </c>
       <c r="T19">
-        <v>2.95</v>
+        <v>2.62</v>
       </c>
       <c r="U19">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="V19">
         <v>1.38</v>
@@ -3442,28 +3442,28 @@
         <v>1.3</v>
       </c>
       <c r="Z19">
-        <v>3.25</v>
+        <v>3.43</v>
       </c>
       <c r="AA19">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="AB19">
+        <v>1.85</v>
+      </c>
+      <c r="AC19">
+        <v>3.4</v>
+      </c>
+      <c r="AD19">
+        <v>1.25</v>
+      </c>
+      <c r="AE19">
+        <v>1.1</v>
+      </c>
+      <c r="AF19">
         <v>1.75</v>
       </c>
-      <c r="AC19">
-        <v>3.39</v>
-      </c>
-      <c r="AD19">
-        <v>1.31</v>
-      </c>
-      <c r="AE19">
-        <v>1.11</v>
-      </c>
-      <c r="AF19">
-        <v>1.76</v>
-      </c>
       <c r="AG19">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>1.26</v>
       </c>
       <c r="AK19">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,34 +3569,34 @@
         </is>
       </c>
       <c r="N20">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="O20">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="P20">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="Q20">
-        <v>4.37</v>
+        <v>4.42</v>
       </c>
       <c r="R20">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="S20">
         <v>1.4</v>
       </c>
       <c r="T20">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="U20">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="V20">
         <v>1.35</v>
       </c>
       <c r="W20">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X20">
         <v>1.02</v>
@@ -3605,16 +3605,16 @@
         <v>1.34</v>
       </c>
       <c r="Z20">
-        <v>3.2</v>
+        <v>3.21</v>
       </c>
       <c r="AA20">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="AB20">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AC20">
-        <v>3.69</v>
+        <v>3.66</v>
       </c>
       <c r="AD20">
         <v>1.27</v>
@@ -3623,10 +3623,10 @@
         <v>1.05</v>
       </c>
       <c r="AF20">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG20">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AK20">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3735,10 +3735,10 @@
         <v>1.95</v>
       </c>
       <c r="O21">
-        <v>3.44</v>
+        <v>3.1</v>
       </c>
       <c r="P21">
-        <v>4.04</v>
+        <v>3.75</v>
       </c>
       <c r="Q21">
         <v>2.78</v>
@@ -3750,46 +3750,46 @@
         <v>1.56</v>
       </c>
       <c r="T21">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="U21">
-        <v>3.4</v>
+        <v>3.26</v>
       </c>
       <c r="V21">
         <v>1.28</v>
       </c>
       <c r="W21">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X21">
         <v>1.04</v>
       </c>
       <c r="Y21">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="Z21">
-        <v>2.59</v>
+        <v>2.69</v>
       </c>
       <c r="AA21">
-        <v>2.6</v>
+        <v>2.32</v>
       </c>
       <c r="AB21">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="AC21">
-        <v>4.43</v>
+        <v>4.34</v>
       </c>
       <c r="AD21">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AE21">
         <v>1.04</v>
       </c>
       <c r="AF21">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="AG21">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="AK21">
         <v>1.78</v>

--- a/jogos_2026-10-07.xlsx
+++ b/jogos_2026-10-07.xlsx
@@ -1489,10 +1489,10 @@
         <v>0</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AC7">
         <v>0</v>
@@ -2105,10 +2105,10 @@
         <v>2.13</v>
       </c>
       <c r="O11">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P11">
-        <v>3.4</v>
+        <v>3.58</v>
       </c>
       <c r="Q11">
         <v>2.7</v>
@@ -2175,7 +2175,7 @@
         <v>1.28</v>
       </c>
       <c r="AK11">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2268,25 +2268,25 @@
         <v>1.79</v>
       </c>
       <c r="O12">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="P12">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="Q12">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="R12">
         <v>2.25</v>
       </c>
       <c r="S12">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T12">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="U12">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="V12">
         <v>1.46</v>
@@ -2298,19 +2298,19 @@
         <v>1.02</v>
       </c>
       <c r="Y12">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="Z12">
-        <v>3.58</v>
+        <v>3.87</v>
       </c>
       <c r="AA12">
         <v>1.85</v>
       </c>
       <c r="AB12">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="AC12">
-        <v>3.1</v>
+        <v>3.03</v>
       </c>
       <c r="AD12">
         <v>1.33</v>
@@ -2434,19 +2434,19 @@
         <v>3.5</v>
       </c>
       <c r="P13">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="Q13">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="R13">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S13">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="T13">
-        <v>2.73</v>
+        <v>3</v>
       </c>
       <c r="U13">
         <v>2.58</v>
@@ -2455,7 +2455,7 @@
         <v>1.43</v>
       </c>
       <c r="W13">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X13">
         <v>1.03</v>
@@ -2467,10 +2467,10 @@
         <v>3.6</v>
       </c>
       <c r="AA13">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AB13">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC13">
         <v>3.25</v>
@@ -2612,7 +2612,7 @@
         <v>2.73</v>
       </c>
       <c r="U14">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="V14">
         <v>1.35</v>
@@ -2630,10 +2630,10 @@
         <v>3.09</v>
       </c>
       <c r="AA14">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AB14">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="AC14">
         <v>3.87</v>
@@ -2664,7 +2664,7 @@
         <v>1.25</v>
       </c>
       <c r="AK14">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2923,7 +2923,7 @@
         <v>3.9</v>
       </c>
       <c r="P16">
-        <v>4.8</v>
+        <v>5.05</v>
       </c>
       <c r="Q16">
         <v>2.15</v>
@@ -2959,7 +2959,7 @@
         <v>1.85</v>
       </c>
       <c r="AB16">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AC16">
         <v>2.97</v>
@@ -3243,37 +3243,37 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.31</v>
+        <v>2.8</v>
       </c>
       <c r="O18">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P18">
-        <v>3.18</v>
+        <v>2.53</v>
       </c>
       <c r="Q18">
-        <v>3.28</v>
+        <v>3.33</v>
       </c>
       <c r="R18">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="S18">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T18">
-        <v>2.86</v>
+        <v>3.2</v>
       </c>
       <c r="U18">
-        <v>2.53</v>
+        <v>2.46</v>
       </c>
       <c r="V18">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W18">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X18">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y18">
         <v>1.19</v>
@@ -3282,10 +3282,10 @@
         <v>3.75</v>
       </c>
       <c r="AA18">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="AB18">
-        <v>1.78</v>
+        <v>1.96</v>
       </c>
       <c r="AC18">
         <v>2.9</v>
@@ -3294,7 +3294,7 @@
         <v>1.36</v>
       </c>
       <c r="AE18">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="AF18">
         <v>1.59</v>
@@ -3316,7 +3316,7 @@
         <v>1.3</v>
       </c>
       <c r="AK18">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.95</v>
+        <v>3.6</v>
       </c>
       <c r="O19">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P19">
-        <v>3.4</v>
+        <v>1.85</v>
       </c>
       <c r="Q19">
-        <v>2.66</v>
+        <v>4.42</v>
       </c>
       <c r="R19">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="S19">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="T19">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="U19">
-        <v>2.91</v>
+        <v>3.04</v>
       </c>
       <c r="V19">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="W19">
+        <v>1.06</v>
+      </c>
+      <c r="X19">
+        <v>1.02</v>
+      </c>
+      <c r="Y19">
+        <v>1.34</v>
+      </c>
+      <c r="Z19">
+        <v>3.21</v>
+      </c>
+      <c r="AA19">
+        <v>2.02</v>
+      </c>
+      <c r="AB19">
+        <v>1.77</v>
+      </c>
+      <c r="AC19">
+        <v>3.66</v>
+      </c>
+      <c r="AD19">
+        <v>1.27</v>
+      </c>
+      <c r="AE19">
         <v>1.05</v>
       </c>
-      <c r="X19">
-        <v>1.03</v>
-      </c>
-      <c r="Y19">
-        <v>1.3</v>
-      </c>
-      <c r="Z19">
-        <v>3.43</v>
-      </c>
-      <c r="AA19">
-        <v>1.96</v>
-      </c>
-      <c r="AB19">
+      <c r="AF19">
         <v>1.85</v>
       </c>
-      <c r="AC19">
-        <v>3.4</v>
-      </c>
-      <c r="AD19">
-        <v>1.25</v>
-      </c>
-      <c r="AE19">
-        <v>1.1</v>
-      </c>
-      <c r="AF19">
-        <v>1.75</v>
-      </c>
       <c r="AG19">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AK19">
-        <v>1.7</v>
+        <v>1.23</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>3.6</v>
+        <v>2.05</v>
       </c>
       <c r="O20">
+        <v>3.1</v>
+      </c>
+      <c r="P20">
         <v>3.4</v>
       </c>
-      <c r="P20">
-        <v>1.85</v>
-      </c>
       <c r="Q20">
-        <v>4.42</v>
+        <v>2.75</v>
       </c>
       <c r="R20">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="S20">
-        <v>1.4</v>
+        <v>1.56</v>
       </c>
       <c r="T20">
-        <v>2.88</v>
+        <v>2.4</v>
       </c>
       <c r="U20">
-        <v>3.04</v>
+        <v>3.26</v>
       </c>
       <c r="V20">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="W20">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X20">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y20">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="Z20">
-        <v>3.21</v>
+        <v>2.65</v>
       </c>
       <c r="AA20">
-        <v>2.02</v>
+        <v>2.53</v>
       </c>
       <c r="AB20">
-        <v>1.77</v>
+        <v>1.52</v>
       </c>
       <c r="AC20">
-        <v>3.66</v>
+        <v>4.38</v>
       </c>
       <c r="AD20">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AE20">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AF20">
-        <v>1.85</v>
+        <v>2.08</v>
       </c>
       <c r="AG20">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AK20">
-        <v>1.23</v>
+        <v>1.67</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G21">
@@ -3735,61 +3735,61 @@
         <v>1.95</v>
       </c>
       <c r="O21">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P21">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="Q21">
-        <v>2.78</v>
+        <v>2.66</v>
       </c>
       <c r="R21">
-        <v>2.03</v>
+        <v>2.23</v>
       </c>
       <c r="S21">
-        <v>1.56</v>
+        <v>1.37</v>
       </c>
       <c r="T21">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="U21">
-        <v>3.26</v>
+        <v>2.91</v>
       </c>
       <c r="V21">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="W21">
+        <v>1.06</v>
+      </c>
+      <c r="X21">
         <v>1.03</v>
       </c>
-      <c r="X21">
-        <v>1.04</v>
-      </c>
       <c r="Y21">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="Z21">
-        <v>2.69</v>
+        <v>3.43</v>
       </c>
       <c r="AA21">
-        <v>2.32</v>
+        <v>1.96</v>
       </c>
       <c r="AB21">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AC21">
-        <v>4.34</v>
+        <v>3.4</v>
       </c>
       <c r="AD21">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AE21">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AF21">
-        <v>2.11</v>
+        <v>1.73</v>
       </c>
       <c r="AG21">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AK21">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>JS El Biar</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G27">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G28">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>JS El Biar</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G29">
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.86</v>
+        <v>1.94</v>
       </c>
       <c r="O30">
-        <v>3.57</v>
+        <v>3.5</v>
       </c>
       <c r="P30">
-        <v>4.47</v>
+        <v>3.9</v>
       </c>
       <c r="Q30">
         <v>2.45</v>
@@ -5217,10 +5217,10 @@
         <v>1.4</v>
       </c>
       <c r="T30">
+        <v>2.9</v>
+      </c>
+      <c r="U30">
         <v>2.66</v>
-      </c>
-      <c r="U30">
-        <v>2.67</v>
       </c>
       <c r="V30">
         <v>1.4</v>
@@ -5238,13 +5238,13 @@
         <v>3.4</v>
       </c>
       <c r="AA30">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="AB30">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AC30">
-        <v>3.4</v>
+        <v>3.43</v>
       </c>
       <c r="AD30">
         <v>1.29</v>
@@ -5256,7 +5256,7 @@
         <v>1.8</v>
       </c>
       <c r="AG30">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>

--- a/jogos_2026-10-07.xlsx
+++ b/jogos_2026-10-07.xlsx
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G26">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G27">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>JS El Biar</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G28">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>JS El Biar</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G29">

--- a/jogos_2026-10-07.xlsx
+++ b/jogos_2026-10-07.xlsx
@@ -2597,7 +2597,7 @@
         <v>3.25</v>
       </c>
       <c r="P14">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="Q14">
         <v>2.6</v>
@@ -2627,22 +2627,22 @@
         <v>1.38</v>
       </c>
       <c r="Z14">
-        <v>3.09</v>
+        <v>2.9</v>
       </c>
       <c r="AA14">
         <v>2.07</v>
       </c>
       <c r="AB14">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="AC14">
-        <v>3.87</v>
+        <v>3.74</v>
       </c>
       <c r="AD14">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AE14">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF14">
         <v>1.93</v>
@@ -2763,55 +2763,55 @@
         <v>0</v>
       </c>
       <c r="Q15">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="R15">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="S15">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="T15">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U15">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="V15">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W15">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X15">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y15">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Z15">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AA15">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AB15">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC15">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="AD15">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AE15">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF15">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG15">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK15">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="N19">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="O19">
         <v>3.4</v>
@@ -3415,10 +3415,10 @@
         <v>1.85</v>
       </c>
       <c r="Q19">
-        <v>4.42</v>
+        <v>4</v>
       </c>
       <c r="R19">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S19">
         <v>1.4</v>
@@ -3448,7 +3448,7 @@
         <v>2.02</v>
       </c>
       <c r="AB19">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AC19">
         <v>3.66</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="O20">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P20">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="Q20">
         <v>2.75</v>
@@ -3596,7 +3596,7 @@
         <v>1.28</v>
       </c>
       <c r="W20">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X20">
         <v>1.04</v>
@@ -3747,16 +3747,16 @@
         <v>2.23</v>
       </c>
       <c r="S21">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="T21">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="U21">
         <v>2.91</v>
       </c>
       <c r="V21">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W21">
         <v>1.06</v>
@@ -3780,7 +3780,7 @@
         <v>3.4</v>
       </c>
       <c r="AD21">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AE21">
         <v>1.1</v>

--- a/jogos_2026-10-07.xlsx
+++ b/jogos_2026-10-07.xlsx
@@ -2763,55 +2763,55 @@
         <v>0</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL15">
         <v>0</v>

--- a/jogos_2026-10-07.xlsx
+++ b/jogos_2026-10-07.xlsx
@@ -2105,34 +2105,34 @@
         <v>2.13</v>
       </c>
       <c r="O11">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P11">
         <v>3.58</v>
       </c>
       <c r="Q11">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="R11">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="S11">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T11">
         <v>2.53</v>
       </c>
       <c r="U11">
-        <v>3.2</v>
+        <v>3.02</v>
       </c>
       <c r="V11">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="W11">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X11">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y11">
         <v>1.33</v>
@@ -2141,25 +2141,25 @@
         <v>3.1</v>
       </c>
       <c r="AA11">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB11">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AC11">
-        <v>3.87</v>
+        <v>3.68</v>
       </c>
       <c r="AD11">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE11">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF11">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AG11">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AK11">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2268,10 +2268,10 @@
         <v>1.79</v>
       </c>
       <c r="O12">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="P12">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="Q12">
         <v>2.3</v>
@@ -2280,16 +2280,16 @@
         <v>2.25</v>
       </c>
       <c r="S12">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="T12">
-        <v>2.82</v>
+        <v>3.22</v>
       </c>
       <c r="U12">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="V12">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="W12">
         <v>1.08</v>
@@ -2298,31 +2298,31 @@
         <v>1.02</v>
       </c>
       <c r="Y12">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="Z12">
-        <v>3.87</v>
+        <v>4.1</v>
       </c>
       <c r="AA12">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AB12">
-        <v>2.03</v>
+        <v>2.07</v>
       </c>
       <c r="AC12">
-        <v>3.03</v>
+        <v>2.88</v>
       </c>
       <c r="AD12">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE12">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF12">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AG12">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AK12">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2431,7 +2431,7 @@
         <v>2.2</v>
       </c>
       <c r="O13">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P13">
         <v>3.1</v>
@@ -2443,19 +2443,19 @@
         <v>2.2</v>
       </c>
       <c r="S13">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T13">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="U13">
-        <v>2.58</v>
+        <v>2.88</v>
       </c>
       <c r="V13">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="W13">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X13">
         <v>1.03</v>
@@ -2467,25 +2467,25 @@
         <v>3.6</v>
       </c>
       <c r="AA13">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AB13">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AC13">
-        <v>3.25</v>
+        <v>3.04</v>
       </c>
       <c r="AD13">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE13">
         <v>1.07</v>
       </c>
       <c r="AF13">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AG13">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>1.3</v>
       </c>
       <c r="AK13">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2923,13 +2923,13 @@
         <v>3.9</v>
       </c>
       <c r="P16">
-        <v>5.05</v>
+        <v>4.75</v>
       </c>
       <c r="Q16">
         <v>2.15</v>
       </c>
       <c r="R16">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="S16">
         <v>1.37</v>
@@ -2938,7 +2938,7 @@
         <v>2.77</v>
       </c>
       <c r="U16">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="V16">
         <v>1.43</v>
@@ -2974,7 +2974,7 @@
         <v>1.8</v>
       </c>
       <c r="AG16">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AK16">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3243,7 +3243,7 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="O18">
         <v>3.5</v>
@@ -3255,7 +3255,7 @@
         <v>3.33</v>
       </c>
       <c r="R18">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="S18">
         <v>1.35</v>
@@ -3273,7 +3273,7 @@
         <v>1.07</v>
       </c>
       <c r="X18">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y18">
         <v>1.19</v>
@@ -3282,16 +3282,16 @@
         <v>3.75</v>
       </c>
       <c r="AA18">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="AB18">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="AC18">
-        <v>2.9</v>
+        <v>2.81</v>
       </c>
       <c r="AD18">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE18">
         <v>1.16</v>
@@ -5208,10 +5208,10 @@
         <v>3.9</v>
       </c>
       <c r="Q30">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="R30">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="S30">
         <v>1.4</v>
@@ -5220,34 +5220,34 @@
         <v>2.9</v>
       </c>
       <c r="U30">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="V30">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W30">
         <v>1.05</v>
       </c>
       <c r="X30">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y30">
         <v>1.27</v>
       </c>
       <c r="Z30">
-        <v>3.4</v>
+        <v>3.14</v>
       </c>
       <c r="AA30">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AB30">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AC30">
         <v>3.43</v>
       </c>
       <c r="AD30">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AE30">
         <v>1.06</v>
@@ -5272,7 +5272,7 @@
         <v>1.31</v>
       </c>
       <c r="AK30">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AL30">
         <v>0</v>

--- a/jogos_2026-10-07.xlsx
+++ b/jogos_2026-10-07.xlsx
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="O7">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P7">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.79</v>
+        <v>2.2</v>
       </c>
       <c r="O12">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="P12">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="Q12">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="R12">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S12">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="T12">
-        <v>3.22</v>
+        <v>2.97</v>
       </c>
       <c r="U12">
-        <v>2.42</v>
+        <v>2.88</v>
       </c>
       <c r="V12">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="W12">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X12">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y12">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="Z12">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="AA12">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="AB12">
-        <v>2.07</v>
+        <v>1.94</v>
       </c>
       <c r="AC12">
-        <v>2.88</v>
+        <v>3.04</v>
       </c>
       <c r="AD12">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AE12">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AF12">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AG12">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK12">
-        <v>2.02</v>
+        <v>1.65</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.2</v>
+        <v>1.79</v>
       </c>
       <c r="O13">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="P13">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="Q13">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="R13">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S13">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="T13">
-        <v>2.97</v>
+        <v>3.22</v>
       </c>
       <c r="U13">
+        <v>2.42</v>
+      </c>
+      <c r="V13">
+        <v>1.48</v>
+      </c>
+      <c r="W13">
+        <v>1.08</v>
+      </c>
+      <c r="X13">
+        <v>1.02</v>
+      </c>
+      <c r="Y13">
+        <v>1.18</v>
+      </c>
+      <c r="Z13">
+        <v>4.1</v>
+      </c>
+      <c r="AA13">
+        <v>1.79</v>
+      </c>
+      <c r="AB13">
+        <v>2.07</v>
+      </c>
+      <c r="AC13">
         <v>2.88</v>
       </c>
-      <c r="V13">
+      <c r="AD13">
         <v>1.36</v>
       </c>
-      <c r="W13">
-        <v>1.06</v>
-      </c>
-      <c r="X13">
-        <v>1.03</v>
-      </c>
-      <c r="Y13">
-        <v>1.25</v>
-      </c>
-      <c r="Z13">
-        <v>3.6</v>
-      </c>
-      <c r="AA13">
-        <v>1.91</v>
-      </c>
-      <c r="AB13">
-        <v>1.94</v>
-      </c>
-      <c r="AC13">
-        <v>3.04</v>
-      </c>
-      <c r="AD13">
-        <v>1.29</v>
-      </c>
       <c r="AE13">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AF13">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AG13">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK13">
-        <v>1.65</v>
+        <v>2.02</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2597,19 +2597,19 @@
         <v>3.25</v>
       </c>
       <c r="P14">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="Q14">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="R14">
         <v>2.05</v>
       </c>
       <c r="S14">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="T14">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="U14">
         <v>2.86</v>
@@ -2618,28 +2618,28 @@
         <v>1.35</v>
       </c>
       <c r="W14">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X14">
         <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="Z14">
-        <v>2.9</v>
+        <v>2.83</v>
       </c>
       <c r="AA14">
         <v>2.07</v>
       </c>
       <c r="AB14">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AC14">
-        <v>3.74</v>
+        <v>3.94</v>
       </c>
       <c r="AD14">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AE14">
         <v>1.02</v>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK14">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2763,55 +2763,55 @@
         <v>0</v>
       </c>
       <c r="Q15">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="R15">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="S15">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="T15">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="U15">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="V15">
         <v>1.32</v>
       </c>
       <c r="W15">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X15">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y15">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="Z15">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="AA15">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="AB15">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AC15">
-        <v>3.79</v>
+        <v>4.2</v>
       </c>
       <c r="AD15">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AE15">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF15">
         <v>1.92</v>
       </c>
       <c r="AG15">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK15">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3406,31 +3406,31 @@
         </is>
       </c>
       <c r="N19">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="O19">
         <v>3.4</v>
       </c>
       <c r="P19">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="Q19">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="R19">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="S19">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="T19">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="U19">
-        <v>3.04</v>
+        <v>2.74</v>
       </c>
       <c r="V19">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W19">
         <v>1.06</v>
@@ -3439,31 +3439,31 @@
         <v>1.02</v>
       </c>
       <c r="Y19">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="Z19">
-        <v>3.21</v>
+        <v>3.13</v>
       </c>
       <c r="AA19">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="AB19">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AC19">
-        <v>3.66</v>
+        <v>3.42</v>
       </c>
       <c r="AD19">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AE19">
         <v>1.05</v>
       </c>
       <c r="AF19">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AG19">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3575,28 +3575,28 @@
         <v>3</v>
       </c>
       <c r="P20">
+        <v>2.99</v>
+      </c>
+      <c r="Q20">
+        <v>2.88</v>
+      </c>
+      <c r="R20">
+        <v>1.91</v>
+      </c>
+      <c r="S20">
+        <v>1.44</v>
+      </c>
+      <c r="T20">
+        <v>2.42</v>
+      </c>
+      <c r="U20">
         <v>3.3</v>
       </c>
-      <c r="Q20">
-        <v>2.75</v>
-      </c>
-      <c r="R20">
-        <v>2.02</v>
-      </c>
-      <c r="S20">
-        <v>1.56</v>
-      </c>
-      <c r="T20">
-        <v>2.4</v>
-      </c>
-      <c r="U20">
-        <v>3.26</v>
-      </c>
       <c r="V20">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W20">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X20">
         <v>1.04</v>
@@ -3608,13 +3608,13 @@
         <v>2.65</v>
       </c>
       <c r="AA20">
-        <v>2.53</v>
+        <v>2.34</v>
       </c>
       <c r="AB20">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AC20">
-        <v>4.38</v>
+        <v>5</v>
       </c>
       <c r="AD20">
         <v>1.17</v>
@@ -3623,7 +3623,7 @@
         <v>1</v>
       </c>
       <c r="AF20">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AG20">
         <v>1.67</v>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AK20">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="O21">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P21">
-        <v>3.4</v>
+        <v>2.87</v>
       </c>
       <c r="Q21">
-        <v>2.66</v>
+        <v>2.56</v>
       </c>
       <c r="R21">
-        <v>2.23</v>
+        <v>2.09</v>
       </c>
       <c r="S21">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T21">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="U21">
-        <v>2.91</v>
+        <v>2.82</v>
       </c>
       <c r="V21">
         <v>1.36</v>
       </c>
       <c r="W21">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z21">
-        <v>3.43</v>
+        <v>3.2</v>
       </c>
       <c r="AA21">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="AB21">
         <v>1.85</v>
       </c>
       <c r="AC21">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="AD21">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE21">
         <v>1.1</v>
       </c>
       <c r="AF21">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AG21">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>1.26</v>
       </c>
       <c r="AK21">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AL21">
         <v>0</v>

--- a/jogos_2026-10-07.xlsx
+++ b/jogos_2026-10-07.xlsx
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G5">
@@ -1133,55 +1133,55 @@
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>5.34</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.6</v>
+        <v>3.05</v>
       </c>
       <c r="O7">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P7">
-        <v>2.41</v>
+        <v>2.11</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -2102,16 +2102,16 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="O11">
         <v>3.2</v>
       </c>
       <c r="P11">
-        <v>3.58</v>
+        <v>3.42</v>
       </c>
       <c r="Q11">
-        <v>2.73</v>
+        <v>2.79</v>
       </c>
       <c r="R11">
         <v>1.98</v>
@@ -2126,10 +2126,10 @@
         <v>3.02</v>
       </c>
       <c r="V11">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="W11">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X11">
         <v>1.02</v>
@@ -2138,44 +2138,44 @@
         <v>1.33</v>
       </c>
       <c r="Z11">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AA11">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AB11">
+        <v>1.72</v>
+      </c>
+      <c r="AC11">
+        <v>3.58</v>
+      </c>
+      <c r="AD11">
+        <v>1.25</v>
+      </c>
+      <c r="AE11">
+        <v>1.05</v>
+      </c>
+      <c r="AF11">
+        <v>1.84</v>
+      </c>
+      <c r="AG11">
+        <v>1.86</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11">
+        <v>1.3</v>
+      </c>
+      <c r="AK11">
         <v>1.67</v>
-      </c>
-      <c r="AC11">
-        <v>3.68</v>
-      </c>
-      <c r="AD11">
-        <v>1.2</v>
-      </c>
-      <c r="AE11">
-        <v>1.03</v>
-      </c>
-      <c r="AF11">
-        <v>1.86</v>
-      </c>
-      <c r="AG11">
-        <v>1.84</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11">
-        <v>1.33</v>
-      </c>
-      <c r="AK11">
-        <v>1.73</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2277,19 +2277,19 @@
         <v>2.7</v>
       </c>
       <c r="R12">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="S12">
         <v>1.33</v>
       </c>
       <c r="T12">
-        <v>2.97</v>
+        <v>2.73</v>
       </c>
       <c r="U12">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="V12">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="W12">
         <v>1.06</v>
@@ -2301,13 +2301,13 @@
         <v>1.25</v>
       </c>
       <c r="Z12">
-        <v>3.6</v>
+        <v>3.73</v>
       </c>
       <c r="AA12">
         <v>1.91</v>
       </c>
       <c r="AB12">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AC12">
         <v>3.04</v>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK12">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2440,16 +2440,16 @@
         <v>2.3</v>
       </c>
       <c r="R13">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="S13">
         <v>1.28</v>
       </c>
       <c r="T13">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="U13">
-        <v>2.42</v>
+        <v>2.39</v>
       </c>
       <c r="V13">
         <v>1.48</v>
@@ -2461,16 +2461,16 @@
         <v>1.02</v>
       </c>
       <c r="Y13">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="Z13">
         <v>4.1</v>
       </c>
       <c r="AA13">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AB13">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="AC13">
         <v>2.88</v>
@@ -2479,10 +2479,10 @@
         <v>1.36</v>
       </c>
       <c r="AE13">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF13">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AG13">
         <v>2.05</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,61 +2591,61 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="O14">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P14">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q14">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="R14">
         <v>2.05</v>
       </c>
       <c r="S14">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T14">
-        <v>2.75</v>
+        <v>2.64</v>
       </c>
       <c r="U14">
-        <v>2.86</v>
+        <v>3.02</v>
       </c>
       <c r="V14">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="W14">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X14">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y14">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z14">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="AA14">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AB14">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AC14">
-        <v>3.94</v>
+        <v>4.2</v>
       </c>
       <c r="AD14">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AE14">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF14">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AG14">
         <v>1.78</v>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AK14">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,61 +2754,61 @@
         </is>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q15">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="R15">
         <v>2.05</v>
       </c>
       <c r="S15">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T15">
-        <v>2.64</v>
+        <v>2.75</v>
       </c>
       <c r="U15">
-        <v>3.02</v>
+        <v>2.86</v>
       </c>
       <c r="V15">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="W15">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X15">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z15">
-        <v>2.9</v>
+        <v>2.83</v>
       </c>
       <c r="AA15">
-        <v>2.13</v>
+        <v>2.07</v>
       </c>
       <c r="AB15">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AC15">
-        <v>4.2</v>
+        <v>3.94</v>
       </c>
       <c r="AD15">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AE15">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF15">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AG15">
         <v>1.78</v>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AK15">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,7 +2917,7 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="O16">
         <v>3.9</v>
@@ -2929,19 +2929,19 @@
         <v>2.15</v>
       </c>
       <c r="R16">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="S16">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="T16">
-        <v>2.77</v>
+        <v>2.88</v>
       </c>
       <c r="U16">
         <v>2.63</v>
       </c>
       <c r="V16">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="W16">
         <v>1.06</v>
@@ -2959,10 +2959,10 @@
         <v>1.85</v>
       </c>
       <c r="AB16">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AC16">
-        <v>2.97</v>
+        <v>3.17</v>
       </c>
       <c r="AD16">
         <v>1.3</v>
@@ -2974,7 +2974,7 @@
         <v>1.8</v>
       </c>
       <c r="AG16">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AK16">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3243,25 +3243,25 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="O18">
         <v>3.5</v>
       </c>
       <c r="P18">
-        <v>2.53</v>
+        <v>2.45</v>
       </c>
       <c r="Q18">
         <v>3.33</v>
       </c>
       <c r="R18">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="S18">
         <v>1.35</v>
       </c>
       <c r="T18">
-        <v>3.2</v>
+        <v>3.27</v>
       </c>
       <c r="U18">
         <v>2.46</v>
@@ -3297,10 +3297,10 @@
         <v>1.16</v>
       </c>
       <c r="AF18">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AG18">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -5202,10 +5202,10 @@
         <v>1.94</v>
       </c>
       <c r="O30">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P30">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Q30">
         <v>2.4</v>
@@ -5214,7 +5214,7 @@
         <v>2.1</v>
       </c>
       <c r="S30">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T30">
         <v>2.9</v>
@@ -5223,10 +5223,10 @@
         <v>2.68</v>
       </c>
       <c r="V30">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W30">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X30">
         <v>1.01</v>
@@ -5241,10 +5241,10 @@
         <v>2</v>
       </c>
       <c r="AB30">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AC30">
-        <v>3.43</v>
+        <v>3.2</v>
       </c>
       <c r="AD30">
         <v>1.26</v>
@@ -5256,7 +5256,7 @@
         <v>1.8</v>
       </c>
       <c r="AG30">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AK30">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="AL30">
         <v>0</v>

--- a/jogos_2026-10-07.xlsx
+++ b/jogos_2026-10-07.xlsx
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="O3">
         <v>3.15</v>
@@ -828,7 +828,7 @@
         <v>1.1</v>
       </c>
       <c r="X3">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y3">
         <v>1.22</v>
@@ -840,7 +840,7 @@
         <v>1.83</v>
       </c>
       <c r="AB3">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AC3">
         <v>2.74</v>
@@ -970,10 +970,10 @@
         <v>2.05</v>
       </c>
       <c r="Q4">
-        <v>4.28</v>
+        <v>3.9</v>
       </c>
       <c r="R4">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="S4">
         <v>1.35</v>
@@ -1133,16 +1133,16 @@
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>5.34</v>
+        <v>5.93</v>
       </c>
       <c r="R5">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="S5">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="T5">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="U5">
         <v>2.32</v>
@@ -1157,31 +1157,31 @@
         <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="Z5">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AA5">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AB5">
-        <v>2.18</v>
+        <v>2.38</v>
       </c>
       <c r="AC5">
-        <v>2.43</v>
+        <v>2.55</v>
       </c>
       <c r="AD5">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AE5">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF5">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG5">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>1.17</v>
       </c>
       <c r="AK5">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2600,10 +2600,10 @@
         <v>0</v>
       </c>
       <c r="Q14">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="R14">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="S14">
         <v>1.41</v>
@@ -2757,22 +2757,22 @@
         <v>1.95</v>
       </c>
       <c r="O15">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P15">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="Q15">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="R15">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="S15">
         <v>1.4</v>
       </c>
       <c r="T15">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="U15">
         <v>2.86</v>
@@ -2781,7 +2781,7 @@
         <v>1.35</v>
       </c>
       <c r="W15">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X15">
         <v>1.01</v>
@@ -2793,7 +2793,7 @@
         <v>2.83</v>
       </c>
       <c r="AA15">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="AB15">
         <v>1.67</v>
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AK15">
         <v>1.8</v>
@@ -3406,16 +3406,16 @@
         </is>
       </c>
       <c r="N19">
-        <v>3.5</v>
+        <v>3.23</v>
       </c>
       <c r="O19">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P19">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="Q19">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="R19">
         <v>2.07</v>
@@ -3427,7 +3427,7 @@
         <v>2.75</v>
       </c>
       <c r="U19">
-        <v>2.74</v>
+        <v>2.79</v>
       </c>
       <c r="V19">
         <v>1.37</v>
@@ -3451,7 +3451,7 @@
         <v>1.73</v>
       </c>
       <c r="AC19">
-        <v>3.42</v>
+        <v>3.7</v>
       </c>
       <c r="AD19">
         <v>1.23</v>
@@ -3575,25 +3575,25 @@
         <v>3</v>
       </c>
       <c r="P20">
-        <v>2.99</v>
+        <v>3.15</v>
       </c>
       <c r="Q20">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="R20">
         <v>1.91</v>
       </c>
       <c r="S20">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="T20">
         <v>2.42</v>
       </c>
       <c r="U20">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="V20">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W20">
         <v>1.05</v>
@@ -3608,10 +3608,10 @@
         <v>2.65</v>
       </c>
       <c r="AA20">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="AB20">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AC20">
         <v>5</v>
@@ -3735,10 +3735,10 @@
         <v>2</v>
       </c>
       <c r="O21">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P21">
-        <v>2.87</v>
+        <v>3.2</v>
       </c>
       <c r="Q21">
         <v>2.56</v>
@@ -3750,7 +3750,7 @@
         <v>1.36</v>
       </c>
       <c r="T21">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="U21">
         <v>2.82</v>

--- a/jogos_2026-10-07.xlsx
+++ b/jogos_2026-10-07.xlsx
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="O7">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="P7">
-        <v>2.11</v>
+        <v>2.23</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AA7">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB7">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>JS El Biar</t>
+          <t>US Biskra</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.3</v>
+        <v>1.61</v>
       </c>
       <c r="O8">
-        <v>2.85</v>
+        <v>3.25</v>
       </c>
       <c r="P8">
-        <v>3.3</v>
+        <v>5.25</v>
       </c>
       <c r="Q8">
-        <v>2.93</v>
+        <v>2.25</v>
       </c>
       <c r="R8">
-        <v>1.98</v>
+        <v>2.03</v>
       </c>
       <c r="S8">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="T8">
-        <v>2.29</v>
+        <v>2.24</v>
       </c>
       <c r="U8">
-        <v>3.15</v>
+        <v>3.58</v>
       </c>
       <c r="V8">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="W8">
         <v>1.03</v>
       </c>
       <c r="X8">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y8">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="Z8">
-        <v>2.46</v>
+        <v>2.41</v>
       </c>
       <c r="AA8">
-        <v>2.35</v>
+        <v>2.49</v>
       </c>
       <c r="AB8">
-        <v>1.51</v>
+        <v>1.42</v>
       </c>
       <c r="AC8">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="AD8">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AE8">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF8">
-        <v>2.01</v>
+        <v>2.42</v>
       </c>
       <c r="AG8">
-        <v>1.7</v>
+        <v>1.49</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AK8">
-        <v>1.52</v>
+        <v>2.07</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>US Biskra</t>
+          <t>JS El Biar</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.61</v>
+        <v>2.3</v>
       </c>
       <c r="O9">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="P9">
-        <v>5.25</v>
+        <v>3.3</v>
       </c>
       <c r="Q9">
-        <v>2.24</v>
+        <v>2.93</v>
       </c>
       <c r="R9">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="S9">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="T9">
-        <v>2.24</v>
+        <v>2.29</v>
       </c>
       <c r="U9">
-        <v>3.58</v>
+        <v>3.15</v>
       </c>
       <c r="V9">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="W9">
         <v>1.03</v>
       </c>
       <c r="X9">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y9">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="Z9">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="AA9">
-        <v>2.54</v>
+        <v>2.37</v>
       </c>
       <c r="AB9">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="AC9">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="AD9">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AE9">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF9">
-        <v>2.42</v>
+        <v>2.01</v>
       </c>
       <c r="AG9">
-        <v>1.49</v>
+        <v>1.7</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AK9">
-        <v>2.07</v>
+        <v>1.52</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1945,13 +1945,13 @@
         <v>4.3</v>
       </c>
       <c r="P10">
-        <v>9.699999999999999</v>
+        <v>8</v>
       </c>
       <c r="Q10">
         <v>1.83</v>
       </c>
       <c r="R10">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="S10">
         <v>1.38</v>
@@ -1966,7 +1966,7 @@
         <v>1.36</v>
       </c>
       <c r="W10">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X10">
         <v>1.02</v>
@@ -1993,7 +1993,7 @@
         <v>1.06</v>
       </c>
       <c r="AF10">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AG10">
         <v>1.48</v>
@@ -2135,7 +2135,7 @@
         <v>1.02</v>
       </c>
       <c r="Y11">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z11">
         <v>3</v>
@@ -2265,19 +2265,19 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="O12">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P12">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q12">
         <v>2.7</v>
       </c>
       <c r="R12">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="S12">
         <v>1.33</v>
@@ -2289,22 +2289,22 @@
         <v>2.8</v>
       </c>
       <c r="V12">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W12">
         <v>1.06</v>
       </c>
       <c r="X12">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y12">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z12">
-        <v>3.73</v>
+        <v>3.71</v>
       </c>
       <c r="AA12">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AB12">
         <v>1.93</v>
@@ -2319,10 +2319,10 @@
         <v>1.07</v>
       </c>
       <c r="AF12">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AG12">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AK12">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2449,7 +2449,7 @@
         <v>3.25</v>
       </c>
       <c r="U13">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="V13">
         <v>1.48</v>
@@ -2464,7 +2464,7 @@
         <v>1.24</v>
       </c>
       <c r="Z13">
-        <v>4.1</v>
+        <v>4.07</v>
       </c>
       <c r="AA13">
         <v>1.78</v>
@@ -2473,7 +2473,7 @@
         <v>2.04</v>
       </c>
       <c r="AC13">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AD13">
         <v>1.36</v>
@@ -2917,7 +2917,7 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="O16">
         <v>3.9</v>
@@ -2950,10 +2950,10 @@
         <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z16">
-        <v>3.42</v>
+        <v>3.8</v>
       </c>
       <c r="AA16">
         <v>1.85</v>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N17">
@@ -3101,16 +3101,16 @@
         <v>3.2</v>
       </c>
       <c r="U17">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="V17">
-        <v>1.58</v>
+        <v>1.73</v>
       </c>
       <c r="W17">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X17">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y17">
         <v>1.15</v>
@@ -3128,13 +3128,13 @@
         <v>2.2</v>
       </c>
       <c r="AD17">
-        <v>1.56</v>
+        <v>1.73</v>
       </c>
       <c r="AE17">
         <v>1.24</v>
       </c>
       <c r="AF17">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AG17">
         <v>1.75</v>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AK17">
-        <v>3.62</v>
+        <v>3.58</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -5205,13 +5205,13 @@
         <v>3.55</v>
       </c>
       <c r="P30">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Q30">
         <v>2.4</v>
       </c>
       <c r="R30">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S30">
         <v>1.36</v>
@@ -5220,7 +5220,7 @@
         <v>2.9</v>
       </c>
       <c r="U30">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="V30">
         <v>1.4</v>
@@ -5232,7 +5232,7 @@
         <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="Z30">
         <v>3.14</v>

--- a/jogos_2026-10-07.xlsx
+++ b/jogos_2026-10-07.xlsx
@@ -801,22 +801,22 @@
         <v>2.45</v>
       </c>
       <c r="O3">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="P3">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="Q3">
-        <v>3.02</v>
+        <v>3.1</v>
       </c>
       <c r="R3">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S3">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T3">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="U3">
         <v>2.5</v>
@@ -837,16 +837,16 @@
         <v>3.58</v>
       </c>
       <c r="AA3">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AB3">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="AC3">
-        <v>2.74</v>
+        <v>3.1</v>
       </c>
       <c r="AD3">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE3">
         <v>1.1</v>
@@ -982,7 +982,7 @@
         <v>2.88</v>
       </c>
       <c r="U4">
-        <v>2.76</v>
+        <v>2.83</v>
       </c>
       <c r="V4">
         <v>1.4</v>
@@ -1133,25 +1133,25 @@
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>5.93</v>
+        <v>5.83</v>
       </c>
       <c r="R5">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S5">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="T5">
         <v>3.4</v>
       </c>
       <c r="U5">
-        <v>2.32</v>
+        <v>2.39</v>
       </c>
       <c r="V5">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="W5">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X5">
         <v>1.01</v>
@@ -1163,25 +1163,25 @@
         <v>4.5</v>
       </c>
       <c r="AA5">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AB5">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AC5">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="AD5">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AE5">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AF5">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AG5">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>1.17</v>
       </c>
       <c r="AK5">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AL5">
         <v>0</v>

--- a/jogos_2026-10-07.xlsx
+++ b/jogos_2026-10-07.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -674,10 +674,10 @@
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC2">
         <v>0</v>
@@ -1625,37 +1625,37 @@
         <v>2.25</v>
       </c>
       <c r="R8">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="S8">
         <v>1.55</v>
       </c>
       <c r="T8">
-        <v>2.24</v>
+        <v>2.37</v>
       </c>
       <c r="U8">
         <v>3.58</v>
       </c>
       <c r="V8">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="W8">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X8">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y8">
         <v>1.48</v>
       </c>
       <c r="Z8">
-        <v>2.41</v>
+        <v>2.63</v>
       </c>
       <c r="AA8">
-        <v>2.49</v>
+        <v>2.55</v>
       </c>
       <c r="AB8">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="AC8">
         <v>5</v>
@@ -1785,7 +1785,7 @@
         <v>3.3</v>
       </c>
       <c r="Q9">
-        <v>2.93</v>
+        <v>2.99</v>
       </c>
       <c r="R9">
         <v>1.98</v>
@@ -1803,7 +1803,7 @@
         <v>1.27</v>
       </c>
       <c r="W9">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X9">
         <v>1.07</v>
@@ -1818,7 +1818,7 @@
         <v>2.37</v>
       </c>
       <c r="AB9">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AC9">
         <v>4.3</v>
@@ -1833,7 +1833,7 @@
         <v>2.01</v>
       </c>
       <c r="AG9">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="AK9">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1951,7 +1951,7 @@
         <v>1.83</v>
       </c>
       <c r="R10">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="S10">
         <v>1.38</v>
@@ -1978,7 +1978,7 @@
         <v>2.97</v>
       </c>
       <c r="AA10">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AB10">
         <v>1.73</v>
@@ -1993,7 +1993,7 @@
         <v>1.06</v>
       </c>
       <c r="AF10">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AG10">
         <v>1.48</v>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="AK10">
         <v>2.92</v>

--- a/jogos_2026-10-07.xlsx
+++ b/jogos_2026-10-07.xlsx
@@ -1664,7 +1664,7 @@
         <v>1.1</v>
       </c>
       <c r="AE8">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF8">
         <v>2.42</v>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="O10">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="P10">
         <v>8</v>
@@ -1993,7 +1993,7 @@
         <v>1.06</v>
       </c>
       <c r="AF10">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AG10">
         <v>1.48</v>
@@ -2120,16 +2120,16 @@
         <v>1.44</v>
       </c>
       <c r="T11">
-        <v>2.53</v>
+        <v>2.75</v>
       </c>
       <c r="U11">
         <v>3.02</v>
       </c>
       <c r="V11">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="W11">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X11">
         <v>1.02</v>
@@ -2141,16 +2141,16 @@
         <v>3</v>
       </c>
       <c r="AA11">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AB11">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AC11">
         <v>3.58</v>
       </c>
       <c r="AD11">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE11">
         <v>1.05</v>
@@ -2268,7 +2268,7 @@
         <v>2.3</v>
       </c>
       <c r="O12">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P12">
         <v>3</v>
@@ -2283,13 +2283,13 @@
         <v>1.33</v>
       </c>
       <c r="T12">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="U12">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="V12">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="W12">
         <v>1.06</v>
@@ -2301,19 +2301,19 @@
         <v>1.29</v>
       </c>
       <c r="Z12">
-        <v>3.71</v>
+        <v>3.73</v>
       </c>
       <c r="AA12">
         <v>1.9</v>
       </c>
       <c r="AB12">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AC12">
         <v>3.04</v>
       </c>
       <c r="AD12">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE12">
         <v>1.07</v>
@@ -2431,16 +2431,16 @@
         <v>1.79</v>
       </c>
       <c r="O13">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P13">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Q13">
         <v>2.3</v>
       </c>
       <c r="R13">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="S13">
         <v>1.28</v>
@@ -2449,10 +2449,10 @@
         <v>3.25</v>
       </c>
       <c r="U13">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="V13">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W13">
         <v>1.08</v>
@@ -2464,7 +2464,7 @@
         <v>1.24</v>
       </c>
       <c r="Z13">
-        <v>4.07</v>
+        <v>4.11</v>
       </c>
       <c r="AA13">
         <v>1.78</v>
@@ -2473,13 +2473,13 @@
         <v>2.04</v>
       </c>
       <c r="AC13">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="AD13">
         <v>1.36</v>
       </c>
       <c r="AE13">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF13">
         <v>1.7</v>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AK13">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,25 +2591,25 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="Q14">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="R14">
         <v>2</v>
       </c>
       <c r="S14">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="T14">
-        <v>2.64</v>
+        <v>2.75</v>
       </c>
       <c r="U14">
         <v>3.02</v>
@@ -2621,13 +2621,13 @@
         <v>1.04</v>
       </c>
       <c r="X14">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y14">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Z14">
-        <v>2.9</v>
+        <v>2.74</v>
       </c>
       <c r="AA14">
         <v>2.13</v>
@@ -2636,16 +2636,16 @@
         <v>1.61</v>
       </c>
       <c r="AC14">
-        <v>4.2</v>
+        <v>3.94</v>
       </c>
       <c r="AD14">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AE14">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF14">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AG14">
         <v>1.78</v>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AK14">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="O15">
+        <v>3.35</v>
+      </c>
+      <c r="P15">
         <v>3.3</v>
       </c>
-      <c r="P15">
-        <v>3.15</v>
-      </c>
       <c r="Q15">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="R15">
         <v>1.92</v>
       </c>
       <c r="S15">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="T15">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
       <c r="U15">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="V15">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W15">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X15">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y15">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="Z15">
-        <v>2.83</v>
+        <v>2.92</v>
       </c>
       <c r="AA15">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="AB15">
         <v>1.67</v>
       </c>
       <c r="AC15">
-        <v>3.94</v>
+        <v>4</v>
       </c>
       <c r="AD15">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="AE15">
         <v>1.02</v>
       </c>
       <c r="AF15">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AG15">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK15">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,10 +2917,10 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="O16">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="P16">
         <v>4.75</v>
@@ -2929,16 +2929,16 @@
         <v>2.15</v>
       </c>
       <c r="R16">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="S16">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="T16">
         <v>2.88</v>
       </c>
       <c r="U16">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="V16">
         <v>1.41</v>
@@ -2953,7 +2953,7 @@
         <v>1.25</v>
       </c>
       <c r="Z16">
-        <v>3.8</v>
+        <v>3.72</v>
       </c>
       <c r="AA16">
         <v>1.85</v>
@@ -2962,7 +2962,7 @@
         <v>1.96</v>
       </c>
       <c r="AC16">
-        <v>3.17</v>
+        <v>2.97</v>
       </c>
       <c r="AD16">
         <v>1.3</v>
@@ -2990,7 +2990,7 @@
         <v>1.17</v>
       </c>
       <c r="AK16">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3252,7 +3252,7 @@
         <v>2.45</v>
       </c>
       <c r="Q18">
-        <v>3.33</v>
+        <v>3.27</v>
       </c>
       <c r="R18">
         <v>2.33</v>
@@ -3261,7 +3261,7 @@
         <v>1.35</v>
       </c>
       <c r="T18">
-        <v>3.27</v>
+        <v>2.96</v>
       </c>
       <c r="U18">
         <v>2.46</v>
@@ -3282,13 +3282,13 @@
         <v>3.75</v>
       </c>
       <c r="AA18">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AB18">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="AC18">
-        <v>2.81</v>
+        <v>2.95</v>
       </c>
       <c r="AD18">
         <v>1.33</v>
@@ -3316,7 +3316,7 @@
         <v>1.3</v>
       </c>
       <c r="AK18">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3409,28 +3409,28 @@
         <v>3.23</v>
       </c>
       <c r="O19">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P19">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="Q19">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="R19">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="S19">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="T19">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="U19">
-        <v>2.79</v>
+        <v>3.02</v>
       </c>
       <c r="V19">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W19">
         <v>1.06</v>
@@ -3442,19 +3442,19 @@
         <v>1.33</v>
       </c>
       <c r="Z19">
-        <v>3.13</v>
+        <v>3.28</v>
       </c>
       <c r="AA19">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AB19">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AC19">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="AD19">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AE19">
         <v>1.05</v>
@@ -3463,7 +3463,7 @@
         <v>1.84</v>
       </c>
       <c r="AG19">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK19">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3605,7 +3605,7 @@
         <v>1.43</v>
       </c>
       <c r="Z20">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="AA20">
         <v>2.35</v>
@@ -3617,7 +3617,7 @@
         <v>5</v>
       </c>
       <c r="AD20">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE20">
         <v>1</v>
@@ -3732,25 +3732,25 @@
         </is>
       </c>
       <c r="N21">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="O21">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P21">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="Q21">
-        <v>2.56</v>
+        <v>2.49</v>
       </c>
       <c r="R21">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="S21">
         <v>1.36</v>
       </c>
       <c r="T21">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="U21">
         <v>2.82</v>
@@ -3759,37 +3759,37 @@
         <v>1.36</v>
       </c>
       <c r="W21">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X21">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y21">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z21">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="AA21">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="AB21">
         <v>1.85</v>
       </c>
       <c r="AC21">
-        <v>3.28</v>
+        <v>3.41</v>
       </c>
       <c r="AD21">
         <v>1.25</v>
       </c>
       <c r="AE21">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF21">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AG21">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>1.26</v>
       </c>
       <c r="AK21">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -5205,10 +5205,10 @@
         <v>3.55</v>
       </c>
       <c r="P30">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Q30">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R30">
         <v>2.15</v>
@@ -5226,25 +5226,25 @@
         <v>1.4</v>
       </c>
       <c r="W30">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X30">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y30">
         <v>1.29</v>
       </c>
       <c r="Z30">
-        <v>3.14</v>
+        <v>3.5</v>
       </c>
       <c r="AA30">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AB30">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AC30">
-        <v>3.2</v>
+        <v>3.48</v>
       </c>
       <c r="AD30">
         <v>1.26</v>
@@ -5256,7 +5256,7 @@
         <v>1.8</v>
       </c>
       <c r="AG30">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>1.21</v>
       </c>
       <c r="AK30">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="AL30">
         <v>0</v>

--- a/jogos_2026-10-07.xlsx
+++ b/jogos_2026-10-07.xlsx
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="O3">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P3">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="Q3">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R3">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="S3">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="T3">
-        <v>3.04</v>
+        <v>2.95</v>
       </c>
       <c r="U3">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="V3">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="W3">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X3">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y3">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z3">
-        <v>3.58</v>
+        <v>3.9</v>
       </c>
       <c r="AA3">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AB3">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="AC3">
-        <v>3.1</v>
+        <v>2.55</v>
       </c>
       <c r="AD3">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AE3">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF3">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="AG3">
-        <v>2.1</v>
+        <v>2.32</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>1.25</v>
       </c>
       <c r="AK3">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -970,25 +970,25 @@
         <v>2.05</v>
       </c>
       <c r="Q4">
-        <v>3.9</v>
+        <v>4.09</v>
       </c>
       <c r="R4">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S4">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="T4">
         <v>2.88</v>
       </c>
       <c r="U4">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="V4">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W4">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X4">
         <v>1.01</v>
@@ -1000,10 +1000,10 @@
         <v>3.28</v>
       </c>
       <c r="AA4">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AB4">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AC4">
         <v>3.2</v>
@@ -1124,16 +1124,16 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Q5">
-        <v>5.83</v>
+        <v>5.61</v>
       </c>
       <c r="R5">
         <v>2.25</v>
@@ -1142,19 +1142,19 @@
         <v>1.28</v>
       </c>
       <c r="T5">
-        <v>3.4</v>
+        <v>3.12</v>
       </c>
       <c r="U5">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="V5">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W5">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X5">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y5">
         <v>1.2</v>
@@ -1166,19 +1166,19 @@
         <v>1.6</v>
       </c>
       <c r="AB5">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AC5">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AD5">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AE5">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF5">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG5">
         <v>2</v>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.17</v>
+        <v>2.4</v>
       </c>
       <c r="AK5">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>8.58</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>5.84</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1450,61 +1450,61 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.8</v>
+        <v>2.46</v>
       </c>
       <c r="O7">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="P7">
-        <v>2.23</v>
+        <v>2.5</v>
       </c>
       <c r="Q7">
-        <v>3.33</v>
+        <v>2.88</v>
       </c>
       <c r="R7">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="S7">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="T7">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="U7">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V7">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="W7">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X7">
         <v>1.02</v>
       </c>
       <c r="Y7">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Z7">
-        <v>5.35</v>
+        <v>5.3</v>
       </c>
       <c r="AA7">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AB7">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AC7">
-        <v>2.06</v>
+        <v>2.13</v>
       </c>
       <c r="AD7">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AE7">
         <v>1.24</v>
       </c>
       <c r="AF7">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AG7">
         <v>2.78</v>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AK7">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1622,16 +1622,16 @@
         <v>5.25</v>
       </c>
       <c r="Q8">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="R8">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="S8">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="T8">
-        <v>2.37</v>
+        <v>1.96</v>
       </c>
       <c r="U8">
         <v>3.58</v>
@@ -1646,47 +1646,47 @@
         <v>1.07</v>
       </c>
       <c r="Y8">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="Z8">
-        <v>2.63</v>
+        <v>2.1</v>
       </c>
       <c r="AA8">
-        <v>2.55</v>
+        <v>2.15</v>
       </c>
       <c r="AB8">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="AC8">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="AD8">
+        <v>1.09</v>
+      </c>
+      <c r="AE8">
+        <v>1.02</v>
+      </c>
+      <c r="AF8">
+        <v>2.1</v>
+      </c>
+      <c r="AG8">
+        <v>1.36</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8">
         <v>1.1</v>
       </c>
-      <c r="AE8">
-        <v>1.04</v>
-      </c>
-      <c r="AF8">
-        <v>2.42</v>
-      </c>
-      <c r="AG8">
-        <v>1.49</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8">
-        <v>1.25</v>
-      </c>
       <c r="AK8">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1779,22 +1779,22 @@
         <v>2.3</v>
       </c>
       <c r="O9">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="P9">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="Q9">
-        <v>2.99</v>
+        <v>2.75</v>
       </c>
       <c r="R9">
-        <v>1.98</v>
+        <v>1.8</v>
       </c>
       <c r="S9">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="T9">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="U9">
         <v>3.15</v>
@@ -1809,31 +1809,31 @@
         <v>1.07</v>
       </c>
       <c r="Y9">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="Z9">
-        <v>2.46</v>
+        <v>2.15</v>
       </c>
       <c r="AA9">
-        <v>2.37</v>
+        <v>2.05</v>
       </c>
       <c r="AB9">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AC9">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="AD9">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AE9">
         <v>1.01</v>
       </c>
       <c r="AF9">
-        <v>2.01</v>
+        <v>1.8</v>
       </c>
       <c r="AG9">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.23</v>
+        <v>1.11</v>
       </c>
       <c r="AK9">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,19 +1939,19 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="O10">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="P10">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="Q10">
         <v>1.83</v>
       </c>
       <c r="R10">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="S10">
         <v>1.38</v>
@@ -1960,7 +1960,7 @@
         <v>2.65</v>
       </c>
       <c r="U10">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="V10">
         <v>1.36</v>
@@ -1972,16 +1972,16 @@
         <v>1.02</v>
       </c>
       <c r="Y10">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z10">
-        <v>2.97</v>
+        <v>3.25</v>
       </c>
       <c r="AA10">
         <v>2.05</v>
       </c>
       <c r="AB10">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AC10">
         <v>3.28</v>
@@ -1993,10 +1993,10 @@
         <v>1.06</v>
       </c>
       <c r="AF10">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="AG10">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AK10">
-        <v>2.92</v>
+        <v>2.74</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,16 +2102,16 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.2</v>
+        <v>2.29</v>
       </c>
       <c r="O11">
         <v>3.2</v>
       </c>
       <c r="P11">
-        <v>3.42</v>
+        <v>3.26</v>
       </c>
       <c r="Q11">
-        <v>2.79</v>
+        <v>2.89</v>
       </c>
       <c r="R11">
         <v>1.98</v>
@@ -2150,7 +2150,7 @@
         <v>3.58</v>
       </c>
       <c r="AD11">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AE11">
         <v>1.05</v>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AK11">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2283,7 +2283,7 @@
         <v>1.33</v>
       </c>
       <c r="T12">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="U12">
         <v>2.81</v>
@@ -2301,7 +2301,7 @@
         <v>1.29</v>
       </c>
       <c r="Z12">
-        <v>3.73</v>
+        <v>3.71</v>
       </c>
       <c r="AA12">
         <v>1.9</v>
@@ -2428,7 +2428,7 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="O13">
         <v>3.7</v>
@@ -2917,7 +2917,7 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="O16">
         <v>3.8</v>
@@ -2929,10 +2929,10 @@
         <v>2.15</v>
       </c>
       <c r="R16">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="S16">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="T16">
         <v>2.88</v>
@@ -2953,7 +2953,7 @@
         <v>1.25</v>
       </c>
       <c r="Z16">
-        <v>3.72</v>
+        <v>3.69</v>
       </c>
       <c r="AA16">
         <v>1.85</v>
@@ -3095,7 +3095,7 @@
         <v>2.5</v>
       </c>
       <c r="S17">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T17">
         <v>3.2</v>
@@ -3104,13 +3104,13 @@
         <v>2.02</v>
       </c>
       <c r="V17">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="W17">
         <v>1.17</v>
       </c>
       <c r="X17">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y17">
         <v>1.15</v>
@@ -3128,7 +3128,7 @@
         <v>2.2</v>
       </c>
       <c r="AD17">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AE17">
         <v>1.24</v>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AK17">
         <v>3.58</v>
@@ -3249,10 +3249,10 @@
         <v>3.5</v>
       </c>
       <c r="P18">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="Q18">
-        <v>3.27</v>
+        <v>3.24</v>
       </c>
       <c r="R18">
         <v>2.33</v>
@@ -3264,10 +3264,10 @@
         <v>2.96</v>
       </c>
       <c r="U18">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="V18">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W18">
         <v>1.07</v>
@@ -3288,7 +3288,7 @@
         <v>2.06</v>
       </c>
       <c r="AC18">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="AD18">
         <v>1.33</v>
@@ -5211,7 +5211,7 @@
         <v>2.38</v>
       </c>
       <c r="R30">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S30">
         <v>1.36</v>
@@ -5244,7 +5244,7 @@
         <v>1.81</v>
       </c>
       <c r="AC30">
-        <v>3.48</v>
+        <v>3.49</v>
       </c>
       <c r="AD30">
         <v>1.26</v>

--- a/jogos_2026-10-07.xlsx
+++ b/jogos_2026-10-07.xlsx
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="O14">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P14">
         <v>3.37</v>
@@ -2754,16 +2754,16 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="O15">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="P15">
-        <v>3.3</v>
+        <v>3.99</v>
       </c>
       <c r="Q15">
-        <v>2.53</v>
+        <v>2.57</v>
       </c>
       <c r="R15">
         <v>1.92</v>
@@ -2775,10 +2775,10 @@
         <v>2.75</v>
       </c>
       <c r="U15">
-        <v>2.82</v>
+        <v>3.17</v>
       </c>
       <c r="V15">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W15">
         <v>1.04</v>
@@ -2790,19 +2790,19 @@
         <v>1.31</v>
       </c>
       <c r="Z15">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="AA15">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="AB15">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AC15">
         <v>4</v>
       </c>
       <c r="AD15">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AE15">
         <v>1.02</v>
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK15">
         <v>1.83</v>
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>3.23</v>
+        <v>3.8</v>
       </c>
       <c r="O19">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P19">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="Q19">
         <v>4.6</v>
@@ -3421,13 +3421,13 @@
         <v>2.1</v>
       </c>
       <c r="S19">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="T19">
         <v>2.8</v>
       </c>
       <c r="U19">
-        <v>3.02</v>
+        <v>3.03</v>
       </c>
       <c r="V19">
         <v>1.36</v>
@@ -3442,7 +3442,7 @@
         <v>1.33</v>
       </c>
       <c r="Z19">
-        <v>3.28</v>
+        <v>3.27</v>
       </c>
       <c r="AA19">
         <v>1.95</v>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK19">
         <v>1.21</v>
@@ -3575,7 +3575,7 @@
         <v>3</v>
       </c>
       <c r="P20">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="Q20">
         <v>2.8</v>
@@ -3605,13 +3605,13 @@
         <v>1.43</v>
       </c>
       <c r="Z20">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="AA20">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="AB20">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AC20">
         <v>5</v>
@@ -3771,19 +3771,19 @@
         <v>3.28</v>
       </c>
       <c r="AA21">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="AB21">
         <v>1.85</v>
       </c>
       <c r="AC21">
-        <v>3.41</v>
+        <v>3.46</v>
       </c>
       <c r="AD21">
         <v>1.25</v>
       </c>
       <c r="AE21">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF21">
         <v>1.78</v>

--- a/jogos_2026-10-07.xlsx
+++ b/jogos_2026-10-07.xlsx
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.31</v>
+        <v>2.45</v>
       </c>
       <c r="O2">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="P2">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA2">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB2">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL2">
         <v>0</v>

--- a/jogos_2026-10-07.xlsx
+++ b/jogos_2026-10-07.xlsx
@@ -798,34 +798,34 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="O3">
         <v>3.35</v>
       </c>
       <c r="P3">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="Q3">
         <v>3</v>
       </c>
       <c r="R3">
-        <v>2.06</v>
+        <v>2.25</v>
       </c>
       <c r="S3">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="T3">
-        <v>2.95</v>
+        <v>3.25</v>
       </c>
       <c r="U3">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="V3">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W3">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X3">
         <v>1.02</v>
@@ -834,7 +834,7 @@
         <v>1.2</v>
       </c>
       <c r="Z3">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AA3">
         <v>1.66</v>
@@ -843,19 +843,19 @@
         <v>2.05</v>
       </c>
       <c r="AC3">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="AD3">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AE3">
         <v>1.14</v>
       </c>
       <c r="AF3">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AG3">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK3">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -964,7 +964,7 @@
         <v>3.5</v>
       </c>
       <c r="O4">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="P4">
         <v>2.05</v>
@@ -1000,7 +1000,7 @@
         <v>3.28</v>
       </c>
       <c r="AA4">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AB4">
         <v>1.85</v>
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>5.6</v>
+        <v>5.15</v>
       </c>
       <c r="O5">
-        <v>4.4</v>
+        <v>4.15</v>
       </c>
       <c r="P5">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="Q5">
         <v>5.61</v>
@@ -1287,19 +1287,19 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="O6">
-        <v>5.55</v>
+        <v>5.75</v>
       </c>
       <c r="P6">
-        <v>8.58</v>
+        <v>9</v>
       </c>
       <c r="Q6">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="R6">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="S6">
         <v>1.22</v>
@@ -1326,10 +1326,10 @@
         <v>5.84</v>
       </c>
       <c r="AA6">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="AB6">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="AC6">
         <v>2.24</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AK6">
-        <v>4.28</v>
+        <v>4</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1453,10 +1453,10 @@
         <v>2.46</v>
       </c>
       <c r="O7">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="P7">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="Q7">
         <v>2.88</v>
@@ -1489,7 +1489,7 @@
         <v>5.3</v>
       </c>
       <c r="AA7">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AB7">
         <v>2.6</v>
@@ -1613,31 +1613,31 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="O8">
         <v>3.25</v>
       </c>
       <c r="P8">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="Q8">
         <v>2.1</v>
       </c>
       <c r="R8">
-        <v>1.83</v>
+        <v>2.07</v>
       </c>
       <c r="S8">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="T8">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="U8">
         <v>3.58</v>
       </c>
       <c r="V8">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="W8">
         <v>1.04</v>
@@ -1776,25 +1776,25 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="O9">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="P9">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="Q9">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="R9">
         <v>1.8</v>
       </c>
       <c r="S9">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="T9">
-        <v>2</v>
+        <v>2.29</v>
       </c>
       <c r="U9">
         <v>3.15</v>
@@ -1939,19 +1939,19 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="O10">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="P10">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="Q10">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="R10">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S10">
         <v>1.38</v>
@@ -1972,31 +1972,31 @@
         <v>1.02</v>
       </c>
       <c r="Y10">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="Z10">
-        <v>3.25</v>
+        <v>2.6</v>
       </c>
       <c r="AA10">
         <v>2.05</v>
       </c>
       <c r="AB10">
-        <v>1.74</v>
+        <v>1.59</v>
       </c>
       <c r="AC10">
-        <v>3.28</v>
+        <v>2.75</v>
       </c>
       <c r="AD10">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AE10">
         <v>1.06</v>
       </c>
       <c r="AF10">
-        <v>2.32</v>
+        <v>2.05</v>
       </c>
       <c r="AG10">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="AK10">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2597,7 +2597,7 @@
         <v>3.1</v>
       </c>
       <c r="P14">
-        <v>3.37</v>
+        <v>3.55</v>
       </c>
       <c r="Q14">
         <v>2.7</v>
@@ -2606,7 +2606,7 @@
         <v>2</v>
       </c>
       <c r="S14">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="T14">
         <v>2.75</v>
@@ -2618,7 +2618,7 @@
         <v>1.32</v>
       </c>
       <c r="W14">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X14">
         <v>1.02</v>
@@ -2763,7 +2763,7 @@
         <v>3.99</v>
       </c>
       <c r="Q15">
-        <v>2.57</v>
+        <v>2.53</v>
       </c>
       <c r="R15">
         <v>1.92</v>
@@ -2775,10 +2775,10 @@
         <v>2.75</v>
       </c>
       <c r="U15">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="V15">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W15">
         <v>1.04</v>
@@ -2793,13 +2793,13 @@
         <v>3</v>
       </c>
       <c r="AA15">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AB15">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AC15">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AD15">
         <v>1.22</v>
@@ -2808,10 +2808,10 @@
         <v>1.02</v>
       </c>
       <c r="AF15">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AG15">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -3412,25 +3412,25 @@
         <v>3.3</v>
       </c>
       <c r="P19">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="Q19">
-        <v>4.6</v>
+        <v>4.74</v>
       </c>
       <c r="R19">
         <v>2.1</v>
       </c>
       <c r="S19">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T19">
         <v>2.8</v>
       </c>
       <c r="U19">
-        <v>3.03</v>
+        <v>3.04</v>
       </c>
       <c r="V19">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W19">
         <v>1.06</v>
@@ -3439,19 +3439,19 @@
         <v>1.02</v>
       </c>
       <c r="Y19">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z19">
-        <v>3.27</v>
+        <v>3.3</v>
       </c>
       <c r="AA19">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="AB19">
         <v>1.75</v>
       </c>
       <c r="AC19">
-        <v>3.65</v>
+        <v>3.69</v>
       </c>
       <c r="AD19">
         <v>1.28</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="O20">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="P20">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="Q20">
         <v>2.8</v>
@@ -3605,7 +3605,7 @@
         <v>1.43</v>
       </c>
       <c r="Z20">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="AA20">
         <v>2.34</v>
@@ -3732,19 +3732,19 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="O21">
         <v>3.3</v>
       </c>
       <c r="P21">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="Q21">
-        <v>2.49</v>
+        <v>2.41</v>
       </c>
       <c r="R21">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="S21">
         <v>1.36</v>
@@ -3759,7 +3759,7 @@
         <v>1.36</v>
       </c>
       <c r="W21">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X21">
         <v>1</v>
@@ -3771,19 +3771,19 @@
         <v>3.28</v>
       </c>
       <c r="AA21">
-        <v>1.98</v>
+        <v>1.88</v>
       </c>
       <c r="AB21">
         <v>1.85</v>
       </c>
       <c r="AC21">
-        <v>3.46</v>
+        <v>3.4</v>
       </c>
       <c r="AD21">
         <v>1.25</v>
       </c>
       <c r="AE21">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF21">
         <v>1.78</v>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK21">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AL21">
         <v>0</v>

--- a/jogos_2026-10-07.xlsx
+++ b/jogos_2026-10-07.xlsx
@@ -638,40 +638,40 @@
         <v>2.45</v>
       </c>
       <c r="O2">
+        <v>3.1</v>
+      </c>
+      <c r="P2">
+        <v>2.5</v>
+      </c>
+      <c r="Q2">
+        <v>3.52</v>
+      </c>
+      <c r="R2">
+        <v>1.86</v>
+      </c>
+      <c r="S2">
+        <v>1.35</v>
+      </c>
+      <c r="T2">
         <v>2.9</v>
       </c>
-      <c r="P2">
+      <c r="U2">
         <v>2.7</v>
       </c>
-      <c r="Q2">
-        <v>3.4</v>
-      </c>
-      <c r="R2">
-        <v>2</v>
-      </c>
-      <c r="S2">
-        <v>1.45</v>
-      </c>
-      <c r="T2">
-        <v>2.58</v>
-      </c>
-      <c r="U2">
-        <v>3</v>
-      </c>
       <c r="V2">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="W2">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X2">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y2">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="Z2">
-        <v>2.83</v>
+        <v>3.14</v>
       </c>
       <c r="AA2">
         <v>2.15</v>
@@ -680,19 +680,19 @@
         <v>1.66</v>
       </c>
       <c r="AC2">
-        <v>3.72</v>
+        <v>3.2</v>
       </c>
       <c r="AD2">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AE2">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF2">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AG2">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="AK2">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -801,7 +801,7 @@
         <v>2.5</v>
       </c>
       <c r="O3">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="P3">
         <v>2.65</v>
@@ -816,16 +816,16 @@
         <v>1.33</v>
       </c>
       <c r="T3">
-        <v>3.25</v>
+        <v>2.95</v>
       </c>
       <c r="U3">
-        <v>2.41</v>
+        <v>2.31</v>
       </c>
       <c r="V3">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="W3">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X3">
         <v>1.02</v>
@@ -834,28 +834,28 @@
         <v>1.2</v>
       </c>
       <c r="Z3">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="AA3">
         <v>1.66</v>
       </c>
       <c r="AB3">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AC3">
-        <v>2.56</v>
+        <v>2.51</v>
       </c>
       <c r="AD3">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AE3">
         <v>1.14</v>
       </c>
       <c r="AF3">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG3">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK3">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
+        <v>5</v>
+      </c>
+      <c r="O4">
+        <v>4.1</v>
+      </c>
+      <c r="P4">
+        <v>1.5</v>
+      </c>
+      <c r="Q4">
+        <v>5.82</v>
+      </c>
+      <c r="R4">
+        <v>2.32</v>
+      </c>
+      <c r="S4">
+        <v>1.25</v>
+      </c>
+      <c r="T4">
         <v>3.5</v>
       </c>
-      <c r="O4">
-        <v>3.25</v>
-      </c>
-      <c r="P4">
-        <v>2.05</v>
-      </c>
-      <c r="Q4">
-        <v>4.09</v>
-      </c>
-      <c r="R4">
-        <v>2.2</v>
-      </c>
-      <c r="S4">
-        <v>1.38</v>
-      </c>
-      <c r="T4">
-        <v>2.88</v>
-      </c>
       <c r="U4">
-        <v>2.8</v>
+        <v>2.27</v>
       </c>
       <c r="V4">
-        <v>1.39</v>
+        <v>1.51</v>
       </c>
       <c r="W4">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X4">
         <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="Z4">
-        <v>3.28</v>
+        <v>5</v>
       </c>
       <c r="AA4">
-        <v>1.96</v>
+        <v>1.5</v>
       </c>
       <c r="AB4">
-        <v>1.85</v>
+        <v>2.4</v>
       </c>
       <c r="AC4">
-        <v>3.2</v>
+        <v>2.45</v>
       </c>
       <c r="AD4">
-        <v>1.26</v>
+        <v>1.53</v>
       </c>
       <c r="AE4">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="AF4">
         <v>1.73</v>
       </c>
       <c r="AG4">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.24</v>
+        <v>2.5</v>
       </c>
       <c r="AK4">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>5.15</v>
+        <v>3.4</v>
       </c>
       <c r="O5">
-        <v>4.15</v>
+        <v>3.25</v>
       </c>
       <c r="P5">
-        <v>1.51</v>
+        <v>2.05</v>
       </c>
       <c r="Q5">
-        <v>5.61</v>
+        <v>4.1</v>
       </c>
       <c r="R5">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="S5">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="T5">
-        <v>3.12</v>
+        <v>2.68</v>
       </c>
       <c r="U5">
-        <v>2.38</v>
+        <v>2.67</v>
       </c>
       <c r="V5">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="W5">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X5">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z5">
-        <v>4.5</v>
+        <v>3.28</v>
       </c>
       <c r="AA5">
-        <v>1.6</v>
+        <v>1.94</v>
       </c>
       <c r="AB5">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AC5">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="AD5">
-        <v>1.44</v>
+        <v>1.26</v>
       </c>
       <c r="AE5">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AF5">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG5">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>2.4</v>
+        <v>1.24</v>
       </c>
       <c r="AK5">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.29</v>
+        <v>2.1</v>
       </c>
       <c r="O11">
         <v>3.2</v>
@@ -2120,7 +2120,7 @@
         <v>1.44</v>
       </c>
       <c r="T11">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="U11">
         <v>3.02</v>
@@ -2138,22 +2138,22 @@
         <v>1.36</v>
       </c>
       <c r="Z11">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AA11">
         <v>2.15</v>
       </c>
       <c r="AB11">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AC11">
         <v>3.58</v>
       </c>
       <c r="AD11">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE11">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF11">
         <v>1.84</v>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AK11">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,16 +2265,16 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="O12">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P12">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="Q12">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="R12">
         <v>2.2</v>
@@ -2283,46 +2283,46 @@
         <v>1.33</v>
       </c>
       <c r="T12">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="U12">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="V12">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W12">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X12">
         <v>1.04</v>
       </c>
       <c r="Y12">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z12">
-        <v>3.71</v>
+        <v>3.82</v>
       </c>
       <c r="AA12">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AB12">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AC12">
-        <v>3.04</v>
+        <v>2.97</v>
       </c>
       <c r="AD12">
         <v>1.3</v>
       </c>
       <c r="AE12">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF12">
         <v>1.67</v>
       </c>
       <c r="AG12">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>1.29</v>
       </c>
       <c r="AK12">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>4.1</v>
       </c>
       <c r="Q13">
+        <v>2.2</v>
+      </c>
+      <c r="R13">
         <v>2.3</v>
       </c>
-      <c r="R13">
-        <v>2.25</v>
-      </c>
       <c r="S13">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T13">
         <v>3.25</v>
@@ -2464,7 +2464,7 @@
         <v>1.24</v>
       </c>
       <c r="Z13">
-        <v>4.11</v>
+        <v>4.16</v>
       </c>
       <c r="AA13">
         <v>1.78</v>
@@ -2473,13 +2473,13 @@
         <v>2.04</v>
       </c>
       <c r="AC13">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="AD13">
         <v>1.36</v>
       </c>
       <c r="AE13">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF13">
         <v>1.7</v>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK13">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2917,28 +2917,28 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="O16">
-        <v>3.8</v>
+        <v>3.63</v>
       </c>
       <c r="P16">
-        <v>4.75</v>
+        <v>4.55</v>
       </c>
       <c r="Q16">
         <v>2.15</v>
       </c>
       <c r="R16">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="S16">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="T16">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="U16">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="V16">
         <v>1.41</v>
@@ -2950,10 +2950,10 @@
         <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z16">
-        <v>3.69</v>
+        <v>3.78</v>
       </c>
       <c r="AA16">
         <v>1.85</v>
@@ -2962,10 +2962,10 @@
         <v>1.96</v>
       </c>
       <c r="AC16">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="AD16">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE16">
         <v>1.08</v>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AK16">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3243,61 +3243,61 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.74</v>
+        <v>2.96</v>
       </c>
       <c r="O18">
         <v>3.5</v>
       </c>
       <c r="P18">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="Q18">
-        <v>3.24</v>
+        <v>3.56</v>
       </c>
       <c r="R18">
-        <v>2.33</v>
+        <v>2.16</v>
       </c>
       <c r="S18">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T18">
-        <v>2.96</v>
+        <v>3.29</v>
       </c>
       <c r="U18">
-        <v>2.44</v>
+        <v>2.37</v>
       </c>
       <c r="V18">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W18">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X18">
         <v>1.02</v>
       </c>
       <c r="Y18">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z18">
-        <v>3.75</v>
+        <v>3.98</v>
       </c>
       <c r="AA18">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AB18">
-        <v>2.06</v>
+        <v>2.13</v>
       </c>
       <c r="AC18">
-        <v>2.94</v>
+        <v>2.75</v>
       </c>
       <c r="AD18">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AE18">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AF18">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AG18">
         <v>2.25</v>
@@ -3316,7 +3316,7 @@
         <v>1.3</v>
       </c>
       <c r="AK18">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -5199,7 +5199,7 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="O30">
         <v>3.55</v>
@@ -5211,7 +5211,7 @@
         <v>2.38</v>
       </c>
       <c r="R30">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S30">
         <v>1.36</v>
@@ -5235,7 +5235,7 @@
         <v>1.29</v>
       </c>
       <c r="Z30">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AA30">
         <v>1.95</v>
@@ -5244,7 +5244,7 @@
         <v>1.81</v>
       </c>
       <c r="AC30">
-        <v>3.49</v>
+        <v>3.53</v>
       </c>
       <c r="AD30">
         <v>1.26</v>
@@ -5272,7 +5272,7 @@
         <v>1.21</v>
       </c>
       <c r="AK30">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AL30">
         <v>0</v>

--- a/jogos_2026-10-07.xlsx
+++ b/jogos_2026-10-07.xlsx
@@ -612,13 +612,13 @@
         </is>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -627,11 +627,11 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2">
@@ -696,12 +696,12 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45+5"]</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["83"]</t>
         </is>
       </c>
       <c r="AJ2">
@@ -775,26 +775,26 @@
         </is>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3">
@@ -859,12 +859,12 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["55"]</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["27", "65", "83", "90+3"]</t>
         </is>
       </c>
       <c r="AJ3">
@@ -877,28 +877,28 @@
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN3">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AO3">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP3">
-        <v>-1</v>
+        <v>23</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AR3">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AS3">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -950,24 +950,24 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4">
         <v>0</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="O4">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="P4">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="Q4">
         <v>5.82</v>
@@ -979,7 +979,7 @@
         <v>1.25</v>
       </c>
       <c r="T4">
-        <v>3.5</v>
+        <v>3.24</v>
       </c>
       <c r="U4">
         <v>2.27</v>
@@ -994,10 +994,10 @@
         <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="Z4">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AA4">
         <v>1.5</v>
@@ -1006,62 +1006,62 @@
         <v>2.4</v>
       </c>
       <c r="AC4">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AD4">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AE4">
         <v>1.16</v>
       </c>
       <c r="AF4">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AG4">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
+          <t>["56"]</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ4">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AK4">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP4">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AQ4">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
@@ -1101,54 +1101,54 @@
         </is>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="O5">
         <v>3.25</v>
       </c>
       <c r="P5">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q5">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="R5">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S5">
         <v>1.36</v>
       </c>
       <c r="T5">
-        <v>2.68</v>
+        <v>2.71</v>
       </c>
       <c r="U5">
         <v>2.67</v>
       </c>
       <c r="V5">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="W5">
         <v>1.06</v>
@@ -1185,46 +1185,46 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["18"]</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["11", "51", "80", "90"]</t>
         </is>
       </c>
       <c r="AJ5">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AK5">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AO5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AP5">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>0.54</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>

--- a/jogos_2026-10-07.xlsx
+++ b/jogos_2026-10-07.xlsx
@@ -1264,130 +1264,130 @@
         </is>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6">
         <v>0</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="O6">
-        <v>5.75</v>
+        <v>6.25</v>
       </c>
       <c r="P6">
         <v>9</v>
       </c>
       <c r="Q6">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="R6">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="S6">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="T6">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="U6">
-        <v>2.12</v>
+        <v>1.9</v>
       </c>
       <c r="V6">
-        <v>1.62</v>
+        <v>1.79</v>
       </c>
       <c r="W6">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="X6">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="Z6">
-        <v>5.84</v>
+        <v>7.2</v>
       </c>
       <c r="AA6">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="AB6">
-        <v>2.37</v>
+        <v>3.25</v>
       </c>
       <c r="AC6">
-        <v>2.24</v>
+        <v>1.76</v>
       </c>
       <c r="AD6">
-        <v>1.6</v>
+        <v>1.99</v>
       </c>
       <c r="AE6">
-        <v>1.21</v>
+        <v>1.41</v>
       </c>
       <c r="AF6">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AG6">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["23", "62"]</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["8", "34"]</t>
         </is>
       </c>
       <c r="AJ6">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="AK6">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="AL6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AN6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AO6">
-        <v>-1</v>
+        <v>24</v>
       </c>
       <c r="AP6">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
@@ -1427,16 +1427,16 @@
         </is>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K7">
         <v>0</v>
@@ -1446,111 +1446,111 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N7">
-        <v>2.46</v>
+        <v>3.05</v>
       </c>
       <c r="O7">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P7">
-        <v>2.4</v>
+        <v>2.09</v>
       </c>
       <c r="Q7">
-        <v>2.88</v>
+        <v>3.07</v>
       </c>
       <c r="R7">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="S7">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="T7">
         <v>4</v>
       </c>
       <c r="U7">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="V7">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="W7">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X7">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z7">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="AA7">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AB7">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="AC7">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="AD7">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AE7">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AF7">
         <v>1.4</v>
       </c>
       <c r="AG7">
-        <v>2.78</v>
+        <v>2.66</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["7"]</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["17", "37"]</t>
         </is>
       </c>
       <c r="AJ7">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AK7">
-        <v>1.47</v>
+        <v>1.22</v>
       </c>
       <c r="AL7">
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO7">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AP7">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AQ7">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AR7">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AS7">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AT7">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="O8">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="P8">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="Q8">
-        <v>2.1</v>
+        <v>2.48</v>
       </c>
       <c r="R8">
-        <v>2.07</v>
+        <v>1.91</v>
       </c>
       <c r="S8">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="T8">
-        <v>1.98</v>
+        <v>1.86</v>
       </c>
       <c r="U8">
-        <v>3.58</v>
+        <v>4.2</v>
       </c>
       <c r="V8">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="W8">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X8">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y8">
-        <v>1.36</v>
+        <v>1.52</v>
       </c>
       <c r="Z8">
         <v>2.1</v>
       </c>
       <c r="AA8">
-        <v>2.15</v>
+        <v>2.92</v>
       </c>
       <c r="AB8">
         <v>1.36</v>
       </c>
       <c r="AC8">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="AD8">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AE8">
         <v>1.02</v>
       </c>
       <c r="AF8">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AG8">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.1</v>
+        <v>1.24</v>
       </c>
       <c r="AK8">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,22 +1776,22 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="O9">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="P9">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="Q9">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="R9">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="S9">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="T9">
         <v>2.29</v>
@@ -1809,31 +1809,31 @@
         <v>1.07</v>
       </c>
       <c r="Y9">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="Z9">
-        <v>2.15</v>
+        <v>2.43</v>
       </c>
       <c r="AA9">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="AB9">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="AC9">
-        <v>3.3</v>
+        <v>4.33</v>
       </c>
       <c r="AD9">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AE9">
         <v>1.01</v>
       </c>
       <c r="AF9">
-        <v>1.8</v>
+        <v>2.04</v>
       </c>
       <c r="AG9">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AK9">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,80 +1939,80 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="O10">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="P10">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="Q10">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="R10">
+        <v>2</v>
+      </c>
+      <c r="S10">
+        <v>1.4</v>
+      </c>
+      <c r="T10">
+        <v>2.58</v>
+      </c>
+      <c r="U10">
+        <v>2.81</v>
+      </c>
+      <c r="V10">
+        <v>1.34</v>
+      </c>
+      <c r="W10">
+        <v>1.06</v>
+      </c>
+      <c r="X10">
+        <v>1.03</v>
+      </c>
+      <c r="Y10">
+        <v>1.25</v>
+      </c>
+      <c r="Z10">
+        <v>3.1</v>
+      </c>
+      <c r="AA10">
         <v>2.1</v>
       </c>
-      <c r="S10">
-        <v>1.38</v>
-      </c>
-      <c r="T10">
-        <v>2.65</v>
-      </c>
-      <c r="U10">
-        <v>2.72</v>
-      </c>
-      <c r="V10">
-        <v>1.36</v>
-      </c>
-      <c r="W10">
+      <c r="AB10">
+        <v>1.65</v>
+      </c>
+      <c r="AC10">
+        <v>2.9</v>
+      </c>
+      <c r="AD10">
+        <v>1.17</v>
+      </c>
+      <c r="AE10">
+        <v>1.05</v>
+      </c>
+      <c r="AF10">
+        <v>1.95</v>
+      </c>
+      <c r="AG10">
+        <v>1.45</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10">
         <v>1.07</v>
       </c>
-      <c r="X10">
-        <v>1.02</v>
-      </c>
-      <c r="Y10">
-        <v>1.22</v>
-      </c>
-      <c r="Z10">
-        <v>2.6</v>
-      </c>
-      <c r="AA10">
-        <v>2.05</v>
-      </c>
-      <c r="AB10">
-        <v>1.59</v>
-      </c>
-      <c r="AC10">
-        <v>2.75</v>
-      </c>
-      <c r="AD10">
-        <v>1.2</v>
-      </c>
-      <c r="AE10">
-        <v>1.06</v>
-      </c>
-      <c r="AF10">
-        <v>2.05</v>
-      </c>
-      <c r="AG10">
-        <v>1.4</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10">
-        <v>1.06</v>
-      </c>
       <c r="AK10">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2597,16 +2597,16 @@
         <v>3.1</v>
       </c>
       <c r="P14">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="Q14">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="R14">
         <v>2</v>
       </c>
       <c r="S14">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="T14">
         <v>2.75</v>
@@ -2621,25 +2621,25 @@
         <v>1.05</v>
       </c>
       <c r="X14">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y14">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z14">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="AA14">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="AB14">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AC14">
-        <v>3.94</v>
+        <v>4.4</v>
       </c>
       <c r="AD14">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE14">
         <v>1.02</v>
@@ -2648,7 +2648,7 @@
         <v>1.95</v>
       </c>
       <c r="AG14">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>1.35</v>
       </c>
       <c r="AK14">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,52 +2754,52 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="O15">
         <v>3.25</v>
       </c>
       <c r="P15">
-        <v>3.99</v>
+        <v>3.91</v>
       </c>
       <c r="Q15">
-        <v>2.53</v>
+        <v>2.7</v>
       </c>
       <c r="R15">
-        <v>1.92</v>
+        <v>2.01</v>
       </c>
       <c r="S15">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="T15">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="U15">
-        <v>3.16</v>
+        <v>3.23</v>
       </c>
       <c r="V15">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W15">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X15">
         <v>1.04</v>
       </c>
       <c r="Y15">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z15">
         <v>3</v>
       </c>
       <c r="AA15">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AB15">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AC15">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AD15">
         <v>1.22</v>
@@ -2808,10 +2808,10 @@
         <v>1.02</v>
       </c>
       <c r="AF15">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AG15">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK15">
         <v>1.83</v>
@@ -3083,34 +3083,34 @@
         <v>1.2</v>
       </c>
       <c r="O17">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="P17">
-        <v>9</v>
+        <v>7.75</v>
       </c>
       <c r="Q17">
         <v>1.65</v>
       </c>
       <c r="R17">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="S17">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T17">
         <v>3.2</v>
       </c>
       <c r="U17">
-        <v>2.02</v>
+        <v>2.11</v>
       </c>
       <c r="V17">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="W17">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X17">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y17">
         <v>1.15</v>
@@ -3119,7 +3119,7 @@
         <v>5</v>
       </c>
       <c r="AA17">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="AB17">
         <v>2.5</v>
@@ -3128,7 +3128,7 @@
         <v>2.2</v>
       </c>
       <c r="AD17">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="AE17">
         <v>1.24</v>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AK17">
-        <v>3.58</v>
+        <v>3.06</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3406,28 +3406,28 @@
         </is>
       </c>
       <c r="N19">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="O19">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P19">
-        <v>1.97</v>
+        <v>1.87</v>
       </c>
       <c r="Q19">
-        <v>4.74</v>
+        <v>4.76</v>
       </c>
       <c r="R19">
         <v>2.1</v>
       </c>
       <c r="S19">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="T19">
         <v>2.8</v>
       </c>
       <c r="U19">
-        <v>3.04</v>
+        <v>3.07</v>
       </c>
       <c r="V19">
         <v>1.37</v>
@@ -3436,25 +3436,25 @@
         <v>1.06</v>
       </c>
       <c r="X19">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y19">
         <v>1.34</v>
       </c>
       <c r="Z19">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="AA19">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="AB19">
         <v>1.75</v>
       </c>
       <c r="AC19">
-        <v>3.69</v>
+        <v>3.6</v>
       </c>
       <c r="AD19">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AE19">
         <v>1.05</v>
@@ -3463,7 +3463,7 @@
         <v>1.84</v>
       </c>
       <c r="AG19">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="O20">
         <v>2.9</v>
@@ -3584,16 +3584,16 @@
         <v>1.91</v>
       </c>
       <c r="S20">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="T20">
         <v>2.42</v>
       </c>
       <c r="U20">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="V20">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W20">
         <v>1.05</v>
@@ -3605,28 +3605,28 @@
         <v>1.43</v>
       </c>
       <c r="Z20">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="AA20">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="AB20">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AC20">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="AD20">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AE20">
         <v>1</v>
       </c>
       <c r="AF20">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AG20">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3732,80 +3732,80 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="O21">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P21">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="Q21">
-        <v>2.41</v>
+        <v>2.31</v>
       </c>
       <c r="R21">
-        <v>2.11</v>
+        <v>2.22</v>
       </c>
       <c r="S21">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T21">
-        <v>2.82</v>
+        <v>3.12</v>
       </c>
       <c r="U21">
-        <v>2.82</v>
+        <v>2.53</v>
       </c>
       <c r="V21">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W21">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X21">
         <v>1</v>
       </c>
       <c r="Y21">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="Z21">
-        <v>3.28</v>
+        <v>3.86</v>
       </c>
       <c r="AA21">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AB21">
-        <v>1.85</v>
+        <v>2.02</v>
       </c>
       <c r="AC21">
-        <v>3.4</v>
+        <v>2.86</v>
       </c>
       <c r="AD21">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AE21">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AF21">
-        <v>1.78</v>
+        <v>1.62</v>
       </c>
       <c r="AG21">
+        <v>2.15</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ21">
+        <v>1.23</v>
+      </c>
+      <c r="AK21">
         <v>1.93</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ21">
-        <v>1.25</v>
-      </c>
-      <c r="AK21">
-        <v>1.87</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -4217,7 +4217,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N24">
@@ -4380,7 +4380,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N25">

--- a/jogos_2026-10-07.xlsx
+++ b/jogos_2026-10-07.xlsx
@@ -1581,139 +1581,139 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>US Biskra</t>
+          <t>JS El Biar</t>
         </is>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8">
         <v>0</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N8">
-        <v>1.75</v>
+        <v>2.3</v>
       </c>
       <c r="O8">
-        <v>3.05</v>
+        <v>2.85</v>
       </c>
       <c r="P8">
-        <v>4.9</v>
+        <v>3.25</v>
       </c>
       <c r="Q8">
-        <v>2.48</v>
+        <v>2.8</v>
       </c>
       <c r="R8">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="S8">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="T8">
+        <v>2.29</v>
+      </c>
+      <c r="U8">
+        <v>3.15</v>
+      </c>
+      <c r="V8">
+        <v>1.27</v>
+      </c>
+      <c r="W8">
+        <v>1.05</v>
+      </c>
+      <c r="X8">
+        <v>1.07</v>
+      </c>
+      <c r="Y8">
+        <v>1.45</v>
+      </c>
+      <c r="Z8">
+        <v>2.43</v>
+      </c>
+      <c r="AA8">
+        <v>2.38</v>
+      </c>
+      <c r="AB8">
+        <v>1.49</v>
+      </c>
+      <c r="AC8">
+        <v>4.33</v>
+      </c>
+      <c r="AD8">
+        <v>1.14</v>
+      </c>
+      <c r="AE8">
+        <v>1.01</v>
+      </c>
+      <c r="AF8">
+        <v>2.04</v>
+      </c>
+      <c r="AG8">
+        <v>1.68</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>["19", "49"]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>["61", "74"]</t>
+        </is>
+      </c>
+      <c r="AJ8">
+        <v>1.2</v>
+      </c>
+      <c r="AK8">
+        <v>1.57</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>6</v>
+      </c>
+      <c r="AN8">
+        <v>8</v>
+      </c>
+      <c r="AO8">
+        <v>10</v>
+      </c>
+      <c r="AP8">
+        <v>15</v>
+      </c>
+      <c r="AQ8">
+        <v>1.4</v>
+      </c>
+      <c r="AR8">
         <v>1.86</v>
       </c>
-      <c r="U8">
-        <v>4.2</v>
-      </c>
-      <c r="V8">
-        <v>1.2</v>
-      </c>
-      <c r="W8">
-        <v>1.03</v>
-      </c>
-      <c r="X8">
-        <v>1.08</v>
-      </c>
-      <c r="Y8">
-        <v>1.52</v>
-      </c>
-      <c r="Z8">
-        <v>2.1</v>
-      </c>
-      <c r="AA8">
-        <v>2.92</v>
-      </c>
-      <c r="AB8">
-        <v>1.36</v>
-      </c>
-      <c r="AC8">
-        <v>3.75</v>
-      </c>
-      <c r="AD8">
-        <v>1.07</v>
-      </c>
-      <c r="AE8">
-        <v>1.02</v>
-      </c>
-      <c r="AF8">
-        <v>2.2</v>
-      </c>
-      <c r="AG8">
-        <v>1.33</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8">
-        <v>1.24</v>
-      </c>
-      <c r="AK8">
-        <v>2</v>
-      </c>
-      <c r="AL8">
-        <v>0</v>
-      </c>
-      <c r="AM8">
-        <v>-1</v>
-      </c>
-      <c r="AN8">
-        <v>-1</v>
-      </c>
-      <c r="AO8">
-        <v>-1</v>
-      </c>
-      <c r="AP8">
-        <v>-1</v>
-      </c>
-      <c r="AQ8">
-        <v>0</v>
-      </c>
-      <c r="AR8">
-        <v>0</v>
-      </c>
       <c r="AS8">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
@@ -1744,139 +1744,139 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>JS El Biar</t>
+          <t>US Biskra</t>
         </is>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H9">
         <v>0</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9">
         <v>0</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L9">
         <v>0</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N9">
-        <v>2.3</v>
+        <v>1.75</v>
       </c>
       <c r="O9">
-        <v>2.85</v>
+        <v>3.05</v>
       </c>
       <c r="P9">
-        <v>3.25</v>
+        <v>4.9</v>
       </c>
       <c r="Q9">
-        <v>2.8</v>
+        <v>2.48</v>
       </c>
       <c r="R9">
+        <v>1.91</v>
+      </c>
+      <c r="S9">
+        <v>1.51</v>
+      </c>
+      <c r="T9">
         <v>1.86</v>
       </c>
-      <c r="S9">
-        <v>1.5</v>
-      </c>
-      <c r="T9">
-        <v>2.29</v>
-      </c>
       <c r="U9">
-        <v>3.15</v>
+        <v>4.2</v>
       </c>
       <c r="V9">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="W9">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X9">
+        <v>1.08</v>
+      </c>
+      <c r="Y9">
+        <v>1.52</v>
+      </c>
+      <c r="Z9">
+        <v>2.1</v>
+      </c>
+      <c r="AA9">
+        <v>2.92</v>
+      </c>
+      <c r="AB9">
+        <v>1.36</v>
+      </c>
+      <c r="AC9">
+        <v>3.75</v>
+      </c>
+      <c r="AD9">
         <v>1.07</v>
       </c>
-      <c r="Y9">
-        <v>1.45</v>
-      </c>
-      <c r="Z9">
-        <v>2.43</v>
-      </c>
-      <c r="AA9">
-        <v>2.38</v>
-      </c>
-      <c r="AB9">
-        <v>1.49</v>
-      </c>
-      <c r="AC9">
-        <v>4.33</v>
-      </c>
-      <c r="AD9">
-        <v>1.14</v>
-      </c>
       <c r="AE9">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF9">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="AG9">
-        <v>1.68</v>
+        <v>1.33</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
+          <t>["37", "51", "56", "73"]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ9">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AK9">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="AL9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN9">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO9">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP9">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         </is>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -1928,14 +1928,14 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10">
         <v>0</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N10">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90+7"]</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
@@ -2018,28 +2018,28 @@
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN10">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO10">
-        <v>-1</v>
+        <v>25</v>
       </c>
       <c r="AP10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>0.87</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
+        <v>2.4</v>
+      </c>
+      <c r="O11">
+        <v>3.03</v>
+      </c>
+      <c r="P11">
+        <v>3.32</v>
+      </c>
+      <c r="Q11">
+        <v>3.12</v>
+      </c>
+      <c r="R11">
+        <v>1.85</v>
+      </c>
+      <c r="S11">
+        <v>1.58</v>
+      </c>
+      <c r="T11">
+        <v>2.35</v>
+      </c>
+      <c r="U11">
+        <v>3.55</v>
+      </c>
+      <c r="V11">
+        <v>1.22</v>
+      </c>
+      <c r="W11">
+        <v>1.01</v>
+      </c>
+      <c r="X11">
+        <v>1.07</v>
+      </c>
+      <c r="Y11">
+        <v>1.53</v>
+      </c>
+      <c r="Z11">
+        <v>2.34</v>
+      </c>
+      <c r="AA11">
+        <v>2.4</v>
+      </c>
+      <c r="AB11">
+        <v>1.44</v>
+      </c>
+      <c r="AC11">
+        <v>4.9</v>
+      </c>
+      <c r="AD11">
+        <v>1.16</v>
+      </c>
+      <c r="AE11">
+        <v>1.02</v>
+      </c>
+      <c r="AF11">
         <v>2.1</v>
       </c>
-      <c r="O11">
-        <v>3.2</v>
-      </c>
-      <c r="P11">
-        <v>3.26</v>
-      </c>
-      <c r="Q11">
-        <v>2.89</v>
-      </c>
-      <c r="R11">
-        <v>1.98</v>
-      </c>
-      <c r="S11">
-        <v>1.44</v>
-      </c>
-      <c r="T11">
-        <v>2.69</v>
-      </c>
-      <c r="U11">
-        <v>3.02</v>
-      </c>
-      <c r="V11">
-        <v>1.32</v>
-      </c>
-      <c r="W11">
-        <v>1.05</v>
-      </c>
-      <c r="X11">
-        <v>1.02</v>
-      </c>
-      <c r="Y11">
-        <v>1.36</v>
-      </c>
-      <c r="Z11">
-        <v>2.9</v>
-      </c>
-      <c r="AA11">
-        <v>2.15</v>
-      </c>
-      <c r="AB11">
-        <v>1.65</v>
-      </c>
-      <c r="AC11">
-        <v>3.58</v>
-      </c>
-      <c r="AD11">
-        <v>1.24</v>
-      </c>
-      <c r="AE11">
-        <v>1.04</v>
-      </c>
-      <c r="AF11">
-        <v>1.84</v>
-      </c>
       <c r="AG11">
-        <v>1.86</v>
+        <v>1.66</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AK11">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="O12">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P12">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="Q12">
         <v>2.5</v>
@@ -2280,16 +2280,16 @@
         <v>2.2</v>
       </c>
       <c r="S12">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T12">
-        <v>2.77</v>
+        <v>2.73</v>
       </c>
       <c r="U12">
-        <v>2.79</v>
+        <v>2.91</v>
       </c>
       <c r="V12">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W12">
         <v>1.07</v>
@@ -2298,19 +2298,19 @@
         <v>1.04</v>
       </c>
       <c r="Y12">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z12">
-        <v>3.82</v>
+        <v>3.77</v>
       </c>
       <c r="AA12">
+        <v>1.9</v>
+      </c>
+      <c r="AB12">
         <v>1.85</v>
       </c>
-      <c r="AB12">
-        <v>1.95</v>
-      </c>
       <c r="AC12">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="AD12">
         <v>1.3</v>
@@ -2319,10 +2319,10 @@
         <v>1.08</v>
       </c>
       <c r="AF12">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AG12">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="AK12">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2431,55 +2431,55 @@
         <v>1.83</v>
       </c>
       <c r="O13">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="P13">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Q13">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="R13">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S13">
         <v>1.3</v>
       </c>
       <c r="T13">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U13">
-        <v>2.39</v>
+        <v>2.33</v>
       </c>
       <c r="V13">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="W13">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X13">
         <v>1.02</v>
       </c>
       <c r="Y13">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="Z13">
-        <v>4.16</v>
+        <v>4.61</v>
       </c>
       <c r="AA13">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="AB13">
-        <v>2.04</v>
+        <v>2.13</v>
       </c>
       <c r="AC13">
-        <v>2.91</v>
+        <v>2.72</v>
       </c>
       <c r="AD13">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AE13">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF13">
         <v>1.7</v>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK13">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2600,40 +2600,40 @@
         <v>3.5</v>
       </c>
       <c r="Q14">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="R14">
         <v>2</v>
       </c>
       <c r="S14">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="T14">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="U14">
-        <v>3.02</v>
+        <v>3.08</v>
       </c>
       <c r="V14">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W14">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X14">
         <v>1.03</v>
       </c>
       <c r="Y14">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="Z14">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AA14">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="AB14">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AC14">
         <v>4.4</v>
@@ -2642,7 +2642,7 @@
         <v>1.18</v>
       </c>
       <c r="AE14">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF14">
         <v>1.95</v>
@@ -2664,7 +2664,7 @@
         <v>1.35</v>
       </c>
       <c r="AK14">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,7 +2754,7 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="O15">
         <v>3.25</v>
@@ -2763,7 +2763,7 @@
         <v>3.91</v>
       </c>
       <c r="Q15">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="R15">
         <v>2.01</v>
@@ -2775,16 +2775,16 @@
         <v>2.67</v>
       </c>
       <c r="U15">
-        <v>3.23</v>
+        <v>3.24</v>
       </c>
       <c r="V15">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W15">
         <v>1.03</v>
       </c>
       <c r="X15">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y15">
         <v>1.33</v>
@@ -2793,16 +2793,16 @@
         <v>3</v>
       </c>
       <c r="AA15">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="AB15">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AC15">
         <v>4</v>
       </c>
       <c r="AD15">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE15">
         <v>1.02</v>
@@ -2811,23 +2811,23 @@
         <v>1.94</v>
       </c>
       <c r="AG15">
+        <v>1.9</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15">
+        <v>1.33</v>
+      </c>
+      <c r="AK15">
         <v>1.8</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15">
-        <v>1.3</v>
-      </c>
-      <c r="AK15">
-        <v>1.83</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,58 +2917,58 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="O16">
-        <v>3.63</v>
+        <v>4.12</v>
       </c>
       <c r="P16">
-        <v>4.55</v>
+        <v>5.7</v>
       </c>
       <c r="Q16">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="R16">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S16">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T16">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="U16">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="V16">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="W16">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X16">
         <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Z16">
-        <v>3.78</v>
+        <v>3.98</v>
       </c>
       <c r="AA16">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB16">
-        <v>1.96</v>
+        <v>2.01</v>
       </c>
       <c r="AC16">
-        <v>2.92</v>
+        <v>2.83</v>
       </c>
       <c r="AD16">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AE16">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF16">
         <v>1.8</v>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AK16">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="O18">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="P18">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="Q18">
-        <v>3.56</v>
+        <v>3.59</v>
       </c>
       <c r="R18">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="S18">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T18">
-        <v>3.29</v>
+        <v>3.31</v>
       </c>
       <c r="U18">
-        <v>2.37</v>
+        <v>2.29</v>
       </c>
       <c r="V18">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W18">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X18">
         <v>1.02</v>
       </c>
       <c r="Y18">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z18">
-        <v>3.98</v>
+        <v>4.4</v>
       </c>
       <c r="AA18">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="AB18">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="AC18">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="AD18">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AE18">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF18">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AG18">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>1.3</v>
       </c>
       <c r="AK18">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3415,7 +3415,7 @@
         <v>1.87</v>
       </c>
       <c r="Q19">
-        <v>4.76</v>
+        <v>4.69</v>
       </c>
       <c r="R19">
         <v>2.1</v>
@@ -3427,10 +3427,10 @@
         <v>2.8</v>
       </c>
       <c r="U19">
-        <v>3.07</v>
+        <v>3.11</v>
       </c>
       <c r="V19">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W19">
         <v>1.06</v>
@@ -3439,13 +3439,13 @@
         <v>1.04</v>
       </c>
       <c r="Y19">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="Z19">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="AA19">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="AB19">
         <v>1.75</v>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK19">
         <v>1.21</v>
@@ -3605,28 +3605,28 @@
         <v>1.43</v>
       </c>
       <c r="Z20">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="AA20">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="AB20">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AC20">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="AD20">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AE20">
         <v>1</v>
       </c>
       <c r="AF20">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AG20">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3741,22 +3741,22 @@
         <v>4.2</v>
       </c>
       <c r="Q21">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="R21">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="S21">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T21">
-        <v>3.12</v>
+        <v>3.22</v>
       </c>
       <c r="U21">
-        <v>2.53</v>
+        <v>2.45</v>
       </c>
       <c r="V21">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W21">
         <v>1.08</v>
@@ -3765,28 +3765,28 @@
         <v>1</v>
       </c>
       <c r="Y21">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z21">
-        <v>3.86</v>
+        <v>4.1</v>
       </c>
       <c r="AA21">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AB21">
-        <v>2.02</v>
+        <v>2.11</v>
       </c>
       <c r="AC21">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="AD21">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AE21">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF21">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG21">
         <v>2.15</v>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK21">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="O30">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P30">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="Q30">
         <v>2.38</v>
@@ -5217,19 +5217,19 @@
         <v>1.36</v>
       </c>
       <c r="T30">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="U30">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="V30">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W30">
         <v>1.05</v>
       </c>
       <c r="X30">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y30">
         <v>1.29</v>
@@ -5238,41 +5238,41 @@
         <v>3.4</v>
       </c>
       <c r="AA30">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AB30">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AC30">
-        <v>3.53</v>
+        <v>3.5</v>
       </c>
       <c r="AD30">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AE30">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF30">
         <v>1.8</v>
       </c>
       <c r="AG30">
+        <v>1.9</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ30">
+        <v>1.22</v>
+      </c>
+      <c r="AK30">
         <v>1.95</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ30">
-        <v>1.21</v>
-      </c>
-      <c r="AK30">
-        <v>1.85</v>
       </c>
       <c r="AL30">
         <v>0</v>
